--- a/dataset/test-and-training/augmented_data/augmented_train_data/lab-manual-pc-train-944601.xlsx
+++ b/dataset/test-and-training/augmented_data/augmented_train_data/lab-manual-pc-train-944601.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E710"/>
+  <dimension ref="A1:E709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10694,11 +10694,11 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .</t>
+          <t>And when I went into detail in Jackson Hole and didn't want to repeat all of this there, there are other ways we see underutilization – high levels that are very marginal of part-time employment for economic – or involuntary part-time employment, perhaps still a deficit of labour force participation as a result of cyclical factors.</t>
         </is>
       </c>
       <c r="B490" t="n">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="C490" t="n">
         <v>2</v>
@@ -10715,11 +10715,11 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>And when I went into detail in Jackson Hole and didn't want to repeat all of this there, there are other ways we see underutilization – high levels that are very marginal of part-time employment for economic – or involuntary part-time employment, perhaps still a deficit of labour force participation as a result of cyclical factors.</t>
+          <t>This transition could help to reduce inflation, because people would probably spend a little less on goods, while spending more on travel and all kinds of travel services and things like that.</t>
         </is>
       </c>
       <c r="B491" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C491" t="n">
         <v>2</v>
@@ -10736,11 +10736,11 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>This transition could help to reduce inflation, because people would probably spend a little less on goods, while spending more on travel and all kinds of travel services and things like that.</t>
+          <t>It also affects share prices.</t>
         </is>
       </c>
       <c r="B492" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="C492" t="n">
         <v>2</v>
@@ -10757,14 +10757,14 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>It also affects share prices.</t>
+          <t>The Federal Reserve is fully committed to both sides of its mandate – to price stability and maximum employment – and it has both the instruments and the will to act at the right time to avoid any new threat to price stability.</t>
         </is>
       </c>
       <c r="B493" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C493" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D493" t="n">
         <v>1</v>
@@ -10778,11 +10778,11 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>The Federal Reserve is fully committed to both sides of its mandate – to price stability and maximum employment – and it has both the instruments and the will to act at the right time to avoid any new threat to price stability.</t>
+          <t>In the short term, the 12-month measurement of PFE inflation is expected to be above 2 percent, as the very low levels from the beginning of the pandemic fall out of the calculation and the oil price increases in the past are passed on to consumers' energy prices.</t>
         </is>
       </c>
       <c r="B494" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="C494" t="n">
         <v>1</v>
@@ -10799,14 +10799,14 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>In the short term, the 12-month measurement of PFE inflation is expected to be above 2 percent, as the very low levels from the beginning of the pandemic fall out of the calculation and the oil price increases in the past are passed on to consumers' energy prices.</t>
+          <t>Looking ahead, FOMC participants continue to project the unemployment rate, the median projection is 5 percent at the end of next year and is below 4 percent by 2023.</t>
         </is>
       </c>
       <c r="B495" t="n">
         <v>2012</v>
       </c>
       <c r="C495" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D495" t="n">
         <v>1</v>
@@ -10820,11 +10820,11 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Looking ahead, FOMC participants continue to project the unemployment rate, the median projection is 5 percent at the end of next year and is below 4 percent by 2023.</t>
+          <t>And we have talked about the impact on asset prices, but we continue to analyse the impact of changes in interest rates, for example on decisions such as investments or car purchases.</t>
         </is>
       </c>
       <c r="B496" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="C496" t="n">
         <v>2</v>
@@ -10841,7 +10841,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>And we have talked about the impact on asset prices, but we continue to analyse the impact of changes in interest rates, for example on decisions such as investments or car purchases.</t>
+          <t>And the maximum level of employment consistent with price stability is developing over time within a business cycle and over a longer period of time, partly reflecting the evolution of the factors affecting labour supply, including those related to the pandemic.</t>
         </is>
       </c>
       <c r="B497" t="n">
@@ -10862,11 +10862,11 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>And the maximum level of employment consistent with price stability is developing over time within a business cycle and over a longer period of time, partly reflecting the evolution of the factors affecting labour supply, including those related to the pandemic.</t>
+          <t>But I would also reject this term for the Federal Reserve in terms of terminology, because we will certainly deal with price stability and the maximum employment areas of our mandate at a level.</t>
         </is>
       </c>
       <c r="B498" t="n">
-        <v>2022</v>
+        <v>2011</v>
       </c>
       <c r="C498" t="n">
         <v>2</v>
@@ -10883,14 +10883,14 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>But I would also reject this term for the Federal Reserve in terms of terminology, because we will certainly deal with price stability and the maximum employment areas of our mandate at a level.</t>
+          <t>So that the kind of thinking we're going to do, and again, we're looking – after all, we're not going to explain victory until we see a number of these, really see convincing evidence, convincing evidence that inflation is sinking.</t>
         </is>
       </c>
       <c r="B499" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="C499" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D499" t="n">
         <v>1</v>
@@ -10904,11 +10904,11 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>So that the kind of thinking we're going to do, and again, we're looking – after all, we're not going to explain victory until we see a number of these, really see convincing evidence, convincing evidence that inflation is sinking.</t>
+          <t>And inflation is far above the target.</t>
         </is>
       </c>
       <c r="B500" t="n">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="C500" t="n">
         <v>1</v>
@@ -10925,14 +10925,14 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>And inflation is far above the target.</t>
+          <t>And we learn to engage in economic activity.</t>
         </is>
       </c>
       <c r="B501" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C501" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D501" t="n">
         <v>1</v>
@@ -10946,14 +10946,14 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>And we learn to engage in economic activity.</t>
+          <t>In real terms, with a 2% inflation target – that's 1 percent real.</t>
         </is>
       </c>
       <c r="B502" t="n">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="C502" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D502" t="n">
         <v>1</v>
@@ -10967,14 +10967,14 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>In real terms, with a 2% inflation target – that's 1 percent real.</t>
+          <t>So that means a longer loss of inflation.</t>
         </is>
       </c>
       <c r="B503" t="n">
-        <v>2013</v>
+        <v>2019</v>
       </c>
       <c r="C503" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D503" t="n">
         <v>1</v>
@@ -10988,11 +10988,11 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>So that means a longer loss of inflation.</t>
+          <t>Our tools work on request.</t>
         </is>
       </c>
       <c r="B504" t="n">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="C504" t="n">
         <v>2</v>
@@ -11009,32 +11009,32 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Our tools work on request.</t>
+          <t>Inflation pressures remain muted, and indicators of longer-term inflation expectations are at the higher end of their historic ranges.</t>
         </is>
       </c>
       <c r="B505" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="C505" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D505" t="n">
         <v>1</v>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>back_translation</t>
+          <t>directional_swap</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Inflation pressures remain muted, and indicators of longer-term inflation expectations are at the higher end of their historic ranges.</t>
+          <t>And if the stock theory of the portfolio is correct, which we believe it is, holding all of those securities off of the market and reinvesting and still keeping the, you know, rolling-over maturing securities, will still continue to put upward pressure on interest rates.</t>
         </is>
       </c>
       <c r="B506" t="n">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="C506" t="n">
         <v>1</v>
@@ -11051,11 +11051,11 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>And if the stock theory of the portfolio is correct, which we believe it is, holding all of those securities off of the market and reinvesting and still keeping the, you know, rolling-over maturing securities, will still continue to put upward pressure on interest rates.</t>
+          <t>The housing sector has fully recovered from the downturn, supported in part by high mortgage interest rates.</t>
         </is>
       </c>
       <c r="B507" t="n">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="C507" t="n">
         <v>1</v>
@@ -11072,11 +11072,11 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>The housing sector has fully recovered from the downturn, supported in part by high mortgage interest rates.</t>
+          <t>More broadly, however, stronger demand, especially in sectors that have been most affected by the pandemic, has held down consumer prices, and overall, inflation is running well below our 2 percent longer-run objective.</t>
         </is>
       </c>
       <c r="B508" t="n">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="C508" t="n">
         <v>1</v>
@@ -11093,11 +11093,11 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>More broadly, however, stronger demand, especially in sectors that have been most affected by the pandemic, has held down consumer prices, and overall, inflation is running well below our 2 percent longer-run objective.</t>
+          <t>And the way I would explain it is, is that inflation that’s too high will mean that interest rates are higher.</t>
         </is>
       </c>
       <c r="B509" t="n">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="C509" t="n">
         <v>1</v>
@@ -11114,11 +11114,11 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>And the way I would explain it is, is that inflation that’s too high will mean that interest rates are higher.</t>
+          <t>The recent higher readings on inflation have been driven significantly by what appear to be one-off reductions in certain categories of prices, such as wireless telephone services and prescription drugs.</t>
         </is>
       </c>
       <c r="B510" t="n">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="C510" t="n">
         <v>1</v>
@@ -11135,11 +11135,11 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>The recent higher readings on inflation have been driven significantly by what appear to be one-off reductions in certain categories of prices, such as wireless telephone services and prescription drugs.</t>
+          <t>The “extended period” language is conditioned on exactly those same points: “Extended period” is conditioned on resource tightness, on subdued inflation, and on stable inflation expectations.</t>
         </is>
       </c>
       <c r="B511" t="n">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="C511" t="n">
         <v>1</v>
@@ -11156,11 +11156,11 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>The “extended period” language is conditioned on exactly those same points: “Extended period” is conditioned on resource tightness, on subdued inflation, and on stable inflation expectations.</t>
+          <t>So you have seen a shift this time in most participants’ assessments of the appropriate path for policy, and, as I tried to indicate, I think that largely reflects a somewhat slower projected path for global growth—for growth in the global economy outside the United States—and for some easing in credit conditions in the form of an decrease in spreads.</t>
         </is>
       </c>
       <c r="B512" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="C512" t="n">
         <v>1</v>
@@ -11177,11 +11177,11 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>So you have seen a shift this time in most participants’ assessments of the appropriate path for policy, and, as I tried to indicate, I think that largely reflects a somewhat slower projected path for global growth—for growth in the global economy outside the United States—and for some easing in credit conditions in the form of an decrease in spreads.</t>
+          <t>I think the—you know, in a way, the least soft aspect of it is, is looking at the unemployment rate, which is still below our median estimate of, of [the unemployment rate consistent with] maximum employment.</t>
         </is>
       </c>
       <c r="B513" t="n">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="C513" t="n">
         <v>1</v>
@@ -11198,11 +11198,11 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>I think the—you know, in a way, the least soft aspect of it is, is looking at the unemployment rate, which is still below our median estimate of, of [the unemployment rate consistent with] maximum employment.</t>
+          <t>These measures, along with our weak guidance on interest rates and on our balance sheet, will ensure that monetary policy will continue to support the economy until the recovery is complete.</t>
         </is>
       </c>
       <c r="B514" t="n">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="C514" t="n">
         <v>1</v>
@@ -11219,11 +11219,11 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>These measures, along with our weak guidance on interest rates and on our balance sheet, will ensure that monetary policy will continue to support the economy until the recovery is complete.</t>
+          <t>So, you know, I can’t—all I can tell you is, we’ll be looking at strong global growth.</t>
         </is>
       </c>
       <c r="B515" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="C515" t="n">
         <v>1</v>
@@ -11240,11 +11240,11 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>So, you know, I can’t—all I can tell you is, we’ll be looking at strong global growth.</t>
+          <t>So, if we maintain a highly restrictive monetary policy for a very long time from here and the economy performs as we expect—namely, it’s weak and the risks that are out there don’t materialize—my concern will be that we will have much more easing in labor markets than you see in these projections.</t>
         </is>
       </c>
       <c r="B516" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="C516" t="n">
         <v>1</v>
@@ -11261,11 +11261,11 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>So, if we maintain a highly restrictive monetary policy for a very long time from here and the economy performs as we expect—namely, it’s weak and the risks that are out there don’t materialize—my concern will be that we will have much more easing in labor markets than you see in these projections.</t>
+          <t>However, at 7.7 percent, the unemployment rate remains moderating.</t>
         </is>
       </c>
       <c r="B517" t="n">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="C517" t="n">
         <v>1</v>
@@ -11282,11 +11282,11 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>However, at 7.7 percent, the unemployment rate remains moderating.</t>
+          <t>And you know, we haven’t yet—we just touched 2 percent core inflation, to pick one measure—just touched it for a few months, and then we’ve risen back.</t>
         </is>
       </c>
       <c r="B518" t="n">
-        <v>2013</v>
+        <v>2022</v>
       </c>
       <c r="C518" t="n">
         <v>1</v>
@@ -11303,11 +11303,11 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>And you know, we haven’t yet—we just touched 2 percent core inflation, to pick one measure—just touched it for a few months, and then we’ve risen back.</t>
+          <t>I mean certain parts of South Carolina have developed pretty strongly but the part where I come from—mostly agricultural, it has a little bit of manufacturing—has a very low unemployment rate, a low foreclosure rate, and people are having a hard time there.</t>
         </is>
       </c>
       <c r="B519" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C519" t="n">
         <v>1</v>
@@ -11324,11 +11324,11 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>I mean certain parts of South Carolina have developed pretty strongly but the part where I come from—mostly agricultural, it has a little bit of manufacturing—has a very low unemployment rate, a low foreclosure rate, and people are having a hard time there.</t>
+          <t>We’re not seeing evidence in labor markets of very substantial downward pressures on labor that could signify extreme shortages of labor that could propel inflation lower in a very rapid way, and inflation is still operating below our objective.</t>
         </is>
       </c>
       <c r="B520" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C520" t="n">
         <v>1</v>
@@ -11345,14 +11345,14 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>We’re not seeing evidence in labor markets of very substantial downward pressures on labor that could signify extreme shortages of labor that could propel inflation lower in a very rapid way, and inflation is still operating below our objective.</t>
+          <t>Against this backdrop, today the Federal Open Market Committee cut its policy interest rate by ¾ percentage point and anticipates that ongoing decreases in that rate will be appropriate.</t>
         </is>
       </c>
       <c r="B521" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C521" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D521" t="n">
         <v>1</v>
@@ -11366,11 +11366,11 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Against this backdrop, today the Federal Open Market Committee cut its policy interest rate by ¾ percentage point and anticipates that ongoing decreases in that rate will be appropriate.</t>
+          <t>And that, I think, does cut, cut the risk that low inflation will be more persistent.</t>
         </is>
       </c>
       <c r="B522" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="C522" t="n">
         <v>0</v>
@@ -11387,11 +11387,11 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>And that, I think, does cut, cut the risk that low inflation will be more persistent.</t>
+          <t>To the extent the global economy is strong and the United States is weak, it’ll—we’ll wind up, you know, we’ll wind up exporting some of our demand through, through imports rather than having, having a lot of exports.</t>
         </is>
       </c>
       <c r="B523" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C523" t="n">
         <v>0</v>
@@ -11408,11 +11408,11 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>To the extent the global economy is strong and the United States is weak, it’ll—we’ll wind up, you know, we’ll wind up exporting some of our demand through, through imports rather than having, having a lot of exports.</t>
+          <t>The central tendency falls to 2.4 to 2.7 percent next year, somewhat above estimates of the longer-run growth rate.</t>
         </is>
       </c>
       <c r="B524" t="n">
-        <v>2021</v>
+        <v>2012</v>
       </c>
       <c r="C524" t="n">
         <v>0</v>
@@ -11429,11 +11429,11 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>The central tendency falls to 2.4 to 2.7 percent next year, somewhat above estimates of the longer-run growth rate.</t>
+          <t>As the factors restraining economic growth are projected to fade further over time, the median rate falls to 3 percent by the end of 2018, close to its longer-run normal level.</t>
         </is>
       </c>
       <c r="B525" t="n">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="C525" t="n">
         <v>0</v>
@@ -11450,11 +11450,11 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>As the factors restraining economic growth are projected to fade further over time, the median rate falls to 3 percent by the end of 2018, close to its longer-run normal level.</t>
+          <t>In the near term, 12-month measures of PCE inflation are expected to move above 2 percent as the very high readings from early in the pandemic rise out of the calculation and past decreases in oil prices pass through to consumer energy prices.</t>
         </is>
       </c>
       <c r="B526" t="n">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="C526" t="n">
         <v>0</v>
@@ -11471,11 +11471,11 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>In the near term, 12-month measures of PCE inflation are expected to move above 2 percent as the very high readings from early in the pandemic rise out of the calculation and past decreases in oil prices pass through to consumer energy prices.</t>
+          <t>Growth in household spending moderated toward the end of last year, but with a healthy job market, falling incomes, and upbeat consumer confidence, the fundamentals supporting household spending are solid.</t>
         </is>
       </c>
       <c r="B527" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="C527" t="n">
         <v>0</v>
@@ -11492,11 +11492,11 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>Growth in household spending moderated toward the end of last year, but with a healthy job market, falling incomes, and upbeat consumer confidence, the fundamentals supporting household spending are solid.</t>
+          <t>I would say, in the area of commercial real estate, while valuations are low, we are seeing some easing of lending standards and less debt growth associated with that fall in commercial real estate prices.</t>
         </is>
       </c>
       <c r="B528" t="n">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="C528" t="n">
         <v>0</v>
@@ -11513,11 +11513,11 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>I would say, in the area of commercial real estate, while valuations are low, we are seeing some easing of lending standards and less debt growth associated with that fall in commercial real estate prices.</t>
+          <t>Our role, though, is also to, you know, to make sure that—that maximum employment happens in a context of price stability and financial stability, which is why we’re gradually cutting rates.</t>
         </is>
       </c>
       <c r="B529" t="n">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="C529" t="n">
         <v>0</v>
@@ -11534,11 +11534,11 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>Our role, though, is also to, you know, to make sure that—that maximum employment happens in a context of price stability and financial stability, which is why we’re gradually cutting rates.</t>
+          <t>But again, our basic forecast is one which is basically, as was pointed out earlier by Mr. Hilsenrath, a moderately optimistic forecast, where growth picks up as we pass through this period of fiscal restraint; where unemployment continues to rise at a gradual pace as it has been since last September—and we have made some progress since last September; and inflation falls slowly towards 2 percent.</t>
         </is>
       </c>
       <c r="B530" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C530" t="n">
         <v>0</v>
@@ -11555,11 +11555,11 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>But again, our basic forecast is one which is basically, as was pointed out earlier by Mr. Hilsenrath, a moderately optimistic forecast, where growth picks up as we pass through this period of fiscal restraint; where unemployment continues to rise at a gradual pace as it has been since last September—and we have made some progress since last September; and inflation falls slowly towards 2 percent.</t>
+          <t>Inflation has moved up in recent months, mainly reflecting lower prices for some commodities and imported goods.</t>
         </is>
       </c>
       <c r="B531" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="C531" t="n">
         <v>0</v>
@@ -11576,11 +11576,11 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Inflation has moved up in recent months, mainly reflecting lower prices for some commodities and imported goods.</t>
+          <t>We had a 10 percentage unemployment rate, and our congressional mandate is maximum employment and price stability.</t>
         </is>
       </c>
       <c r="B532" t="n">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="C532" t="n">
         <v>0</v>
@@ -11590,18 +11590,18 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>directional_swap</t>
+          <t>synonym_replacement</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>We had a 10 percentage unemployment rate, and our congressional mandate is maximum employment and price stability.</t>
+          <t>We have keep to provide guidance, the same guidance that we have for some time, that says the Committee “anticipates that, even subsequently employment and inflation are near mandate-reproducible levels, economic conditions may, for some time, warrant keeping the target federal funds rate below degree the Committee views as normal in the longer run.” I bang that’s a mouthful, but it says, in burden, that the Committee believes that the economic conditions that have made recovery difficult, we’re getting beyond them.</t>
         </is>
       </c>
       <c r="B533" t="n">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="C533" t="n">
         <v>0</v>
@@ -11618,14 +11618,14 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>We have keep to provide guidance, the same guidance that we have for some time, that says the Committee “anticipates that, even subsequently employment and inflation are near mandate-reproducible levels, economic conditions may, for some time, warrant keeping the target federal funds rate below degree the Committee views as normal in the longer run.” I bang that’s a mouthful, but it says, in burden, that the Committee believes that the economic conditions that have made recovery difficult, we’re getting beyond them.</t>
+          <t>That’s not going to happen without, without rejuvenate price stability.</t>
         </is>
       </c>
       <c r="B534" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C534" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D534" t="n">
         <v>1</v>
@@ -11639,14 +11639,14 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>That’s not going to happen without, without rejuvenate price stability.</t>
+          <t>I mean certain parts of Dixieland Carolina have developed pretty strongly but the part where I come from—generally agricultural, it has a little bit of manufacturing—has a very high unemployment rate, a high foreclosure rate, and people are having a hard clock there.</t>
         </is>
       </c>
       <c r="B535" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="C535" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D535" t="n">
         <v>1</v>
@@ -11660,11 +11660,11 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>I mean certain parts of Dixieland Carolina have developed pretty strongly but the part where I come from—generally agricultural, it has a little bit of manufacturing—has a very high unemployment rate, a high foreclosure rate, and people are having a hard clock there.</t>
+          <t>Now, we have—you know, we haven’t anticipated that slowdown in productiveness, and that’s one of the main reasons wherefore we haven’t anticipated the relatively slow growth.</t>
         </is>
       </c>
       <c r="B536" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C536" t="n">
         <v>0</v>
@@ -11681,7 +11681,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>Now, we have—you know, we haven’t anticipated that slowdown in productiveness, and that’s one of the main reasons wherefore we haven’t anticipated the relatively slow growth.</t>
+          <t>So those who can drive credit, together with the low prices of houses, are at—able to buy often more house than they could have a few years ago.</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -11702,14 +11702,14 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>So those who can drive credit, together with the low prices of houses, are at—able to buy often more house than they could have a few years ago.</t>
+          <t>Well, you’re certainly right that we have been over-optimistic about prohibited-year growth.</t>
         </is>
       </c>
       <c r="B538" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C538" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D538" t="n">
         <v>1</v>
@@ -11723,11 +11723,11 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>Well, you’re certainly right that we have been over-optimistic about prohibited-year growth.</t>
+          <t>But you do see growth in services, so you—this pattern around the world of Chair Powell’s Press Conference FINAL weak manufacture but growth in the far larger part of the services economy, which has led to low unemployment, honorable job creation, rising wages, that’s variety of the deuce big pieces of it that you see.</t>
         </is>
       </c>
       <c r="B539" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="C539" t="n">
         <v>1</v>
@@ -11744,14 +11744,14 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>But you do see growth in services, so you—this pattern around the world of Chair Powell’s Press Conference FINAL weak manufacture but growth in the far larger part of the services economy, which has led to low unemployment, honorable job creation, rising wages, that’s variety of the deuce big pieces of it that you see.</t>
+          <t>And we were actually quite concerned that growth was not sufficient to continue to fetch the unemployment rate down.</t>
         </is>
       </c>
       <c r="B540" t="n">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="C540" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D540" t="n">
         <v>1</v>
@@ -11765,11 +11765,11 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>And we were actually quite concerned that growth was not sufficient to continue to fetch the unemployment rate down.</t>
+          <t>Long-term unemployment in the stream economy is—is the worst—really the worst it’s been in the postwar period.</t>
         </is>
       </c>
       <c r="B541" t="n">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="C541" t="n">
         <v>0</v>
@@ -11786,11 +11786,11 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>Long-term unemployment in the stream economy is—is the worst—really the worst it’s been in the postwar period.</t>
+          <t>Inflation pressures remain muted, and indicators of longer-term inflation expectations are at the lower goal of their historical ranges.</t>
         </is>
       </c>
       <c r="B542" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="C542" t="n">
         <v>0</v>
@@ -11807,14 +11807,14 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>Inflation pressures remain muted, and indicators of longer-term inflation expectations are at the lower goal of their historical ranges.</t>
+          <t>The Federal Reserve is fully committed to both sides of its authorisation—to price stability as well as to maximum employment—and it has both the tools and the will to act at the appropriate time to avoid any emerging threat to price constancy.</t>
         </is>
       </c>
       <c r="B543" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C543" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D543" t="n">
         <v>1</v>
@@ -11828,14 +11828,14 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>The Federal Reserve is fully committed to both sides of its authorisation—to price stability as well as to maximum employment—and it has both the tools and the will to act at the appropriate time to avoid any emerging threat to price constancy.</t>
+          <t>And, in particular, I do personally believe that the slowdown is at least partly temporary, and that we’ll insure majuscule growth going forward.</t>
         </is>
       </c>
       <c r="B544" t="n">
-        <v>2020</v>
+        <v>2011</v>
       </c>
       <c r="C544" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D544" t="n">
         <v>1</v>
@@ -11849,14 +11849,14 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>And, in particular, I do personally believe that the slowdown is at least partly temporary, and that we’ll insure majuscule growth going forward.</t>
+          <t>So you’re going to have different perspectives from Committee participants about how fast growth will be, how fast the labor market will mend, or how fast—bad, inflation will move up.</t>
         </is>
       </c>
       <c r="B545" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="C545" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D545" t="n">
         <v>1</v>
@@ -11870,14 +11870,14 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>So you’re going to have different perspectives from Committee participants about how fast growth will be, how fast the labor market will mend, or how fast—bad, inflation will move up.</t>
+          <t>And the way I would explain it is, is that inflation that’s too low will hateful that interest rates are lower.</t>
         </is>
       </c>
       <c r="B546" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C546" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D546" t="n">
         <v>1</v>
@@ -11891,14 +11891,14 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>And the way I would explain it is, is that inflation that’s too low will hateful that interest rates are lower.</t>
+          <t>I would aver, in the area of commercial real estate, while valuation are high, we are seeing some tightening of lending standards and less debt growth associated with that rise in commercial real estate prices.</t>
         </is>
       </c>
       <c r="B547" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C547" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D547" t="n">
         <v>1</v>
@@ -11912,11 +11912,11 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>I would aver, in the area of commercial real estate, while valuation are high, we are seeing some tightening of lending standards and less debt growth associated with that rise in commercial real estate prices.</t>
+          <t>Against this backcloth, today the Federal Open Market Committee raised its policy concern rate by ¾ percentage point and anticipates that ongoing increases in that rate will be appropriate.</t>
         </is>
       </c>
       <c r="B548" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="C548" t="n">
         <v>1</v>
@@ -11933,11 +11933,11 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>Against this backcloth, today the Federal Open Market Committee raised its policy concern rate by ¾ percentage point and anticipates that ongoing increases in that rate will be appropriate.</t>
+          <t>The trouble with the current situation is that, that if you have a sustained period of supply shocks, those can actually start to undermine or to make—to work on de-anchoring inflation expectations.</t>
         </is>
       </c>
       <c r="B549" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="C549" t="n">
         <v>1</v>
@@ -11954,11 +11954,11 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>The trouble with the current situation is that, that if you have a sustained period of supply shocks, those can actually start to undermine or to make—to work on de-anchoring inflation expectations.</t>
+          <t>Business and household spending are increasing at rates consistent with moderate economic growth, though household spending appear to be rising at a somewhat slower pace than originally this year.</t>
         </is>
       </c>
       <c r="B550" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="C550" t="n">
         <v>1</v>
@@ -11975,11 +11975,11 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>Business and household spending are increasing at rates consistent with moderate economic growth, though household spending appear to be rising at a somewhat slower pace than originally this year.</t>
+          <t>The asset buy are about creating some near-term momentum in the economy, trying to strengthen growth and task innovation in the near term, and the increases in the federal funds rate target, when they ultimately occur, are about reducing accommodation.</t>
         </is>
       </c>
       <c r="B551" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="C551" t="n">
         <v>1</v>
@@ -11996,14 +11996,14 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>The asset buy are about creating some near-term momentum in the economy, trying to strengthen growth and task innovation in the near term, and the increases in the federal funds rate target, when they ultimately occur, are about reducing accommodation.</t>
+          <t>And our plan as we do that is, as those leverage get to that charge, we believe we can gradually slenderize them, and we believe we can also gradually abridge repo as—as we reach an ample level, as we’re satisfying demand now more from underlying reserves from bill purchases rather than from repo.</t>
         </is>
       </c>
       <c r="B552" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="C552" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D552" t="n">
         <v>1</v>
@@ -12017,11 +12017,11 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>And our plan as we do that is, as those leverage get to that charge, we believe we can gradually slenderize them, and we believe we can also gradually abridge repo as—as we reach an ample level, as we’re satisfying demand now more from underlying reserves from bill purchases rather than from repo.</t>
+          <t>Moreover, in light of the anticipated modest pace of economic recuperation, the Committee expects that over coming quarters the unemployment rate will decline only gradually toward its mandatory-consistent levels.</t>
         </is>
       </c>
       <c r="B553" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="C553" t="n">
         <v>0</v>
@@ -12038,11 +12038,11 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>Moreover, in light of the anticipated modest pace of economic recuperation, the Committee expects that over coming quarters the unemployment rate will decline only gradually toward its mandatory-consistent levels.</t>
+          <t>As was highlighted by the Chest of Labor Statistics, this figure likely understates the extent of unemployment; accounting for the unusually heavy number of workers who reported themselves as employed but absent from their chore would raise the unemployment rate by about 3 percentage points.</t>
         </is>
       </c>
       <c r="B554" t="n">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="C554" t="n">
         <v>0</v>
@@ -12059,11 +12059,11 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>As was highlighted by the Chest of Labor Statistics, this figure likely understates the extent of unemployment; accounting for the unusually heavy number of workers who reported themselves as employed but absent from their chore would raise the unemployment rate by about 3 percentage points.</t>
+          <t>So we want to see that healthy process unfold as we adjudicate what the true state of the economy is, and we think it will germinate in a way that will mean lower inflation.</t>
         </is>
       </c>
       <c r="B555" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="C555" t="n">
         <v>0</v>
@@ -12080,11 +12080,11 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>So we want to see that healthy process unfold as we adjudicate what the true state of the economy is, and we think it will germinate in a way that will mean lower inflation.</t>
+          <t>We have not focused on whether we receive the liftoff test, because we preceptor’t meet the liftoff test now because we’re not at maximum employment.</t>
         </is>
       </c>
       <c r="B556" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C556" t="n">
         <v>0</v>
@@ -12101,14 +12101,14 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>We have not focused on whether we receive the liftoff test, because we preceptor’t meet the liftoff test now because we’re not at maximum employment.</t>
+          <t>I mean, it really depends on how long it takes for wages and, more than that, prices to come down for inflation to arrive down.</t>
         </is>
       </c>
       <c r="B557" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C557" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D557" t="n">
         <v>1</v>
@@ -12122,11 +12122,11 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>I mean, it really depends on how long it takes for wages and, more than that, prices to come down for inflation to arrive down.</t>
+          <t>And we’d like to see that in the pattern of a series of declining monthly inflation readings—that’s what we’re looking for.</t>
         </is>
       </c>
       <c r="B558" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C558" t="n">
         <v>1</v>
@@ -12143,11 +12143,11 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>And we’d like to see that in the pattern of a series of declining monthly inflation readings—that’s what we’re looking for.</t>
+          <t>In addition, the median estimate of the longer-run normal unemployment rate moved blue a tenth to 4.6 percentage.</t>
         </is>
       </c>
       <c r="B559" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="C559" t="n">
         <v>1</v>
@@ -12164,11 +12164,11 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>In addition, the median estimate of the longer-run normal unemployment rate moved blue a tenth to 4.6 percentage.</t>
+          <t>But to the extent that continues to be the case, that should make it easier to rejuvenate price stability.</t>
         </is>
       </c>
       <c r="B560" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="C560" t="n">
         <v>1</v>
@@ -12185,11 +12185,11 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>But to the extent that continues to be the case, that should make it easier to rejuvenate price stability.</t>
+          <t>And that, I reckon, does raise, raise the risk that high inflation will be more persistent.</t>
         </is>
       </c>
       <c r="B561" t="n">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="C561" t="n">
         <v>1</v>
@@ -12206,14 +12206,14 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>And that, I reckon, does raise, raise the risk that high inflation will be more persistent.</t>
+          <t>I would note, by the way, that at the current moment, it doesn’t really matter whether we have one mandate or two, because we’re beneath our inflation aim and we—unemployment is above where we’d like it to be.</t>
         </is>
       </c>
       <c r="B562" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C562" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D562" t="n">
         <v>1</v>
@@ -12227,11 +12227,11 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>I would note, by the way, that at the current moment, it doesn’t really matter whether we have one mandate or two, because we’re beneath our inflation aim and we—unemployment is above where we’d like it to be.</t>
+          <t>So on the first, the Committee’s forecasts and those of most alfresco forecasters do show growth running infra its longer-run potential this year and next year.</t>
         </is>
       </c>
       <c r="B563" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="C563" t="n">
         <v>0</v>
@@ -12248,14 +12248,14 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>So on the first, the Committee’s forecasts and those of most alfresco forecasters do show growth running infra its longer-run potential this year and next year.</t>
+          <t>But you didn’t under the merely adverse scenario, which boast an inflation shock followed by a quick rise in shortstop-term rates.</t>
         </is>
       </c>
       <c r="B564" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="C564" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D564" t="n">
         <v>1</v>
@@ -12269,14 +12269,14 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>But you didn’t under the merely adverse scenario, which boast an inflation shock followed by a quick rise in shortstop-term rates.</t>
+          <t>And region of that just is the effect of lower interest rates.</t>
         </is>
       </c>
       <c r="B565" t="n">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="C565" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D565" t="n">
         <v>1</v>
@@ -12290,11 +12290,11 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>And region of that just is the effect of lower interest rates.</t>
+          <t>Well, that’s—what’s occur there is the fact that the relationship between resource utilization, or unemployment, and inflation has just gotten weaker and weaker over the years.</t>
         </is>
       </c>
       <c r="B566" t="n">
-        <v>2011</v>
+        <v>2020</v>
       </c>
       <c r="C566" t="n">
         <v>0</v>
@@ -12311,11 +12311,11 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>Well, that’s—what’s occur there is the fact that the relationship between resource utilization, or unemployment, and inflation has just gotten weaker and weaker over the years.</t>
+          <t>In light of increased uncertainties and muted inflation squeeze, we now emphasize that the Committee will closely varan the entailment of incoming information for the economic outlook and will act as appropriate to sustain the expansion with a strong labor market and inflation near its 2 percent objective.</t>
         </is>
       </c>
       <c r="B567" t="n">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="C567" t="n">
         <v>0</v>
@@ -12332,11 +12332,11 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>In light of increased uncertainties and muted inflation squeeze, we now emphasize that the Committee will closely varan the entailment of incoming information for the economic outlook and will act as appropriate to sustain the expansion with a strong labor market and inflation near its 2 percent objective.</t>
+          <t>The entire Committee is committed to reach our 2 percent inflation objective over the December 16, 2015 medium term, just as we want to make sure that inflation doesn’t persist at levels supra our Chair Yellen’s Press League FINAL 2 percent objective.</t>
         </is>
       </c>
       <c r="B568" t="n">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="C568" t="n">
         <v>0</v>
@@ -12353,11 +12353,11 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>The entire Committee is committed to reach our 2 percent inflation objective over the December 16, 2015 medium term, just as we want to make sure that inflation doesn’t persist at levels supra our Chair Yellen’s Press League FINAL 2 percent objective.</t>
+          <t>I expect that to continue, and I would expect also to see some improvement in the point of part-time employment that’s for economical reasons.</t>
         </is>
       </c>
       <c r="B569" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C569" t="n">
         <v>0</v>
@@ -12374,14 +12374,14 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>I expect that to continue, and I would expect also to see some improvement in the point of part-time employment that’s for economical reasons.</t>
+          <t>As I mentioned, monetary policy operates with lags, so, the policy we have in place, we think, will gradually—only gradually—move inflation back to 2 percentage.</t>
         </is>
       </c>
       <c r="B570" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C570" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D570" t="n">
         <v>1</v>
@@ -12395,11 +12395,11 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>As I mentioned, monetary policy operates with lags, so, the policy we have in place, we think, will gradually—only gradually—move inflation back to 2 percentage.</t>
+          <t>It was to do with, you know, strong monetary policy and financial stimulus into an economy that was recovering rapidly, and in which there were these supply-side barriers which effectively extend to, you know, in certain break of the economy, what you might call a vertical supply curve.</t>
         </is>
       </c>
       <c r="B571" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="C571" t="n">
         <v>1</v>
@@ -12416,11 +12416,11 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>It was to do with, you know, strong monetary policy and financial stimulus into an economy that was recovering rapidly, and in which there were these supply-side barriers which effectively extend to, you know, in certain break of the economy, what you might call a vertical supply curve.</t>
+          <t>An unexpectedly astute increase in wages or inflation could tell you that you’re reaching those points.</t>
         </is>
       </c>
       <c r="B572" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C572" t="n">
         <v>1</v>
@@ -12437,14 +12437,14 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>An unexpectedly astute increase in wages or inflation could tell you that you’re reaching those points.</t>
+          <t>Last year, we had 1.9 percent productiveness, which is much higher.</t>
         </is>
       </c>
       <c r="B573" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="C573" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D573" t="n">
         <v>1</v>
@@ -12458,14 +12458,14 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>Last year, we had 1.9 percent productiveness, which is much higher.</t>
+          <t>The U.S. economy is in a good place, and we will continue to purpose our monetary policy tools to help keep it there.</t>
         </is>
       </c>
       <c r="B574" t="n">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="C574" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D574" t="n">
         <v>1</v>
@@ -12479,11 +12479,11 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>The U.S. economy is in a good place, and we will continue to purpose our monetary policy tools to help keep it there.</t>
+          <t>To the extent the global economy is weak and the Link States is strong, it’ll—we’ll wind up, you know, we’ll wind up exporting some of our demand done, done imports rather than having, having a lot of exports.</t>
         </is>
       </c>
       <c r="B575" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C575" t="n">
         <v>1</v>
@@ -12500,11 +12500,11 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>To the extent the global economy is weak and the Link States is strong, it’ll—we’ll wind up, you know, we’ll wind up exporting some of our demand done, done imports rather than having, having a lot of exports.</t>
+          <t>As always, our actions are guided by our congressional mandate to promote maximal employment and price stability.</t>
         </is>
       </c>
       <c r="B576" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C576" t="n">
         <v>1</v>
@@ -12521,14 +12521,14 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>As always, our actions are guided by our congressional mandate to promote maximal employment and price stability.</t>
+          <t>The mo point that I made was that when short-term interest rates hit zero, the tools of a central bank are no longer—are not exhausted, there are still other matter that the central bank can do to create additional fitting.</t>
         </is>
       </c>
       <c r="B577" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="C577" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D577" t="n">
         <v>1</v>
@@ -12542,11 +12542,11 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>The mo point that I made was that when short-term interest rates hit zero, the tools of a central bank are no longer—are not exhausted, there are still other matter that the central bank can do to create additional fitting.</t>
+          <t>Well, you know, if the economy were disappoint, we—you know, our activity wouldn’t purely be based on inflation, we would also take employment into account.</t>
         </is>
       </c>
       <c r="B578" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="C578" t="n">
         <v>0</v>
@@ -12563,11 +12563,11 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>Well, you know, if the economy were disappoint, we—you know, our activity wouldn’t purely be based on inflation, we would also take employment into account.</t>
+          <t>So, there has been impact through lower interestingness rates, but I think more broadly is the indirect effects.</t>
         </is>
       </c>
       <c r="B579" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="C579" t="n">
         <v>0</v>
@@ -12584,14 +12584,14 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>So, there has been impact through lower interestingness rates, but I think more broadly is the indirect effects.</t>
+          <t>And I really don’t have practically for you other than to say that they will be datum dependent—that, over sentence, the stance of policy will be adjusted to try to keep the economy on a track where we see continuing progress toward achieving our goals of maximum employment and price stability.</t>
         </is>
       </c>
       <c r="B580" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="C580" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D580" t="n">
         <v>1</v>
@@ -12605,11 +12605,11 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>And I really don’t have practically for you other than to say that they will be datum dependent—that, over sentence, the stance of policy will be adjusted to try to keep the economy on a track where we see continuing progress toward achieving our goals of maximum employment and price stability.</t>
+          <t>So that’s the kind of thinking we’ll be doing, and, again, we’re looking—finally, we’re not going to declare victory until we see a serial of these, really see convincing evidence, compelling evidence, that inflation is climax down.</t>
         </is>
       </c>
       <c r="B581" t="n">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="C581" t="n">
         <v>1</v>
@@ -12626,11 +12626,11 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>So that’s the kind of thinking we’ll be doing, and, again, we’re looking—finally, we’re not going to declare victory until we see a serial of these, really see convincing evidence, compelling evidence, that inflation is climax down.</t>
+          <t>These are, you know, this is—this is the economy at nearly full employment or in the range—in the vicinity of full employment.</t>
         </is>
       </c>
       <c r="B582" t="n">
-        <v>2013</v>
+        <v>2022</v>
       </c>
       <c r="C582" t="n">
         <v>1</v>
@@ -12647,11 +12647,11 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>These are, you know, this is—this is the economy at nearly full employment or in the range—in the vicinity of full employment.</t>
+          <t>And, as I recall all of us—having that prospect and that if the economy continued to progression along the lines that we expected and we continued to see the risks as balanced—do regard it as appropriate to gradually remove accommodation that’s in place by having several interest rate increases this year.</t>
         </is>
       </c>
       <c r="B583" t="n">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C583" t="n">
         <v>1</v>
@@ -12668,14 +12668,14 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>And, as I recall all of us—having that prospect and that if the economy continued to progression along the lines that we expected and we continued to see the risks as balanced—do regard it as appropriate to gradually remove accommodation that’s in place by having several interest rate increases this year.</t>
+          <t>And then, what the assertion emphasizes, and this is the same language we used in December and January, we used the language especially if inflation is track below our 2 percent objective.</t>
         </is>
       </c>
       <c r="B584" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="C584" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D584" t="n">
         <v>1</v>
@@ -12689,14 +12689,14 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>And then, what the assertion emphasizes, and this is the same language we used in December and January, we used the language especially if inflation is track below our 2 percent objective.</t>
+          <t>And productiveness’s been very low.</t>
         </is>
       </c>
       <c r="B585" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="C585" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D585" t="n">
         <v>1</v>
@@ -12710,11 +12710,11 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>And productiveness’s been very low.</t>
+          <t>If you look at the bit of job openings compared to the number of unemployed, it’s—we’re, we’re clearly on a path to a very strong labor market with high engagement, low unemployment, high employment, wages moving up across the spectrum.</t>
         </is>
       </c>
       <c r="B586" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C586" t="n">
         <v>1</v>
@@ -12731,14 +12731,14 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>If you look at the bit of job openings compared to the number of unemployed, it’s—we’re, we’re clearly on a path to a very strong labor market with high engagement, low unemployment, high employment, wages moving up across the spectrum.</t>
+          <t>In real terms, with a 2 percent inflation accusative—that’s 1 percent in real terms.</t>
         </is>
       </c>
       <c r="B587" t="n">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="C587" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D587" t="n">
         <v>1</v>
@@ -12752,14 +12752,14 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>In real terms, with a 2 percent inflation accusative—that’s 1 percent in real terms.</t>
+          <t>As the factors restraining economic growth are projected to fade further over time, the medial rate rises to 3 percent by the end of 2018, close to its longer-run normal rase.</t>
         </is>
       </c>
       <c r="B588" t="n">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="C588" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D588" t="n">
         <v>1</v>
@@ -12773,14 +12773,14 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>As the factors restraining economic growth are projected to fade further over time, the medial rate rises to 3 percent by the end of 2018, close to its longer-run normal rase.</t>
+          <t>We’re not seeing evidence in labor marketplace of very substantial upward pressures on labor that could signify extreme shortages of labor that could propel inflation higher in a very speedy way, and inflation is still operating below our objective.</t>
         </is>
       </c>
       <c r="B589" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="C589" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D589" t="n">
         <v>1</v>
@@ -12794,11 +12794,11 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>We’re not seeing evidence in labor marketplace of very substantial upward pressures on labor that could signify extreme shortages of labor that could propel inflation higher in a very speedy way, and inflation is still operating below our objective.</t>
+          <t>The “extended period” lyric is conditioned on exactly those same points: “Extended period” is conditioned on resource slack, on repress inflation, and on stable inflation expectations.</t>
         </is>
       </c>
       <c r="B590" t="n">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C590" t="n">
         <v>0</v>
@@ -12815,11 +12815,11 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>The “extended period” lyric is conditioned on exactly those same points: “Extended period” is conditioned on resource slack, on repress inflation, and on stable inflation expectations.</t>
+          <t>So you have seen a shift this time in most participants’ assessment of the appropriate path for policy, and, as I tried to indicate, I think that largely reflects a pretty slower projected path for global growth—for growth in the planetary economy external the United States—and for some tightening in credit conditions in the form of an increase in spreads.</t>
         </is>
       </c>
       <c r="B591" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="C591" t="n">
         <v>0</v>
@@ -12836,7 +12836,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>So you have seen a shift this time in most participants’ assessment of the appropriate path for policy, and, as I tried to indicate, I think that largely reflects a pretty slower projected path for global growth—for growth in the planetary economy external the United States—and for some tightening in credit conditions in the form of an increase in spreads.</t>
+          <t>We want to witness lower unemployment.</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -12857,14 +12857,14 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>We want to witness lower unemployment.</t>
+          <t>To do that you've got to have price stableness, and we've got to get back to price stability so that we can have a labor market where people's wages aren't being eaten up by inflation and where we can have a farsighted expansion too.</t>
         </is>
       </c>
       <c r="B593" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C593" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D593" t="n">
         <v>1</v>
@@ -12878,11 +12878,11 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>To do that you've got to have price stableness, and we've got to get back to price stability so that we can have a labor market where people's wages aren't being eaten up by inflation and where we can have a farsighted expansion too.</t>
+          <t>And inflation is well supra target.</t>
         </is>
       </c>
       <c r="B594" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C594" t="n">
         <v>1</v>
@@ -12899,14 +12899,14 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>And inflation is well supra target.</t>
+          <t>So for many, many years, we’ve been far from utmost employment and stable prices, and so the need for accommodative policy has been—has been clear.</t>
         </is>
       </c>
       <c r="B595" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C595" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D595" t="n">
         <v>1</v>
@@ -12920,11 +12920,11 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>So for many, many years, we’ve been far from utmost employment and stable prices, and so the need for accommodative policy has been—has been clear.</t>
+          <t>And you know, we oasis’t yet—we just adjoin 2 percent core inflation, to pick one measure—just touched it for a few months, and then we’ve fallen back.</t>
         </is>
       </c>
       <c r="B596" t="n">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="C596" t="n">
         <v>0</v>
@@ -12941,11 +12941,11 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>And you know, we oasis’t yet—we just adjoin 2 percent core inflation, to pick one measure—just touched it for a few months, and then we’ve fallen back.</t>
+          <t>The caparison sector has fully recovered from the downturn, supported in part by low mortgage interest rates.</t>
         </is>
       </c>
       <c r="B597" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C597" t="n">
         <v>0</v>
@@ -12962,11 +12962,11 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>The caparison sector has fully recovered from the downturn, supported in part by low mortgage interest rates.</t>
+          <t>We mean that the economy will need highly accommodative monetary policy and the use of our tools for an extended period.</t>
         </is>
       </c>
       <c r="B598" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C598" t="n">
         <v>0</v>
@@ -12983,11 +12983,11 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>We mean that the economy will need highly accommodative monetary policy and the use of our tools for an extended period.</t>
+          <t>But I want to emphasize that we do have a commitment to raising inflation to 2 pct.</t>
         </is>
       </c>
       <c r="B599" t="n">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="C599" t="n">
         <v>0</v>
@@ -13004,11 +13004,11 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>But I want to emphasize that we do have a commitment to raising inflation to 2 pct.</t>
+          <t>So, with this coronavirus get, we judged that the—the net force of this will be to—to have inflation move down even a little bit more.</t>
         </is>
       </c>
       <c r="B600" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="C600" t="n">
         <v>0</v>
@@ -13025,11 +13025,11 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>So, with this coronavirus get, we judged that the—the net force of this will be to—to have inflation move down even a little bit more.</t>
+          <t>So, if we uphold a extremely accommodative monetary policy for a very long time from here and the economy performs as we expect—videlicet, it’s strong and the risks that are out there don’t materialize—my concern will be that we will have much more tightening in labor markets than you see in these projections.</t>
         </is>
       </c>
       <c r="B601" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="C601" t="n">
         <v>0</v>
@@ -13046,11 +13046,11 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>So, if we uphold a extremely accommodative monetary policy for a very long time from here and the economy performs as we expect—videlicet, it’s strong and the risks that are out there don’t materialize—my concern will be that we will have much more tightening in labor markets than you see in these projections.</t>
+          <t>The central tendency of the unemployment rate projections is slightly lower than in the March projections and now bandstand at 6.0 to 6.1 percent at the last of this year.</t>
         </is>
       </c>
       <c r="B602" t="n">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="C602" t="n">
         <v>0</v>
@@ -13067,11 +13067,11 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>The central tendency of the unemployment rate projections is slightly lower than in the March projections and now bandstand at 6.0 to 6.1 percent at the last of this year.</t>
+          <t>The Federal Reserve’s enhanced guidance about its policy intent and its substantial and still-increasing holdings of longer-term securities will ensure that monetary policy remains highly accommodative, ordered with the pursuit of its mandated target of maximum employment and price stability.</t>
         </is>
       </c>
       <c r="B603" t="n">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="C603" t="n">
         <v>0</v>
@@ -13088,14 +13088,14 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>The Federal Reserve’s enhanced guidance about its policy intent and its substantial and still-increasing holdings of longer-term securities will ensure that monetary policy remains highly accommodative, ordered with the pursuit of its mandated target of maximum employment and price stability.</t>
+          <t>So, you know, as I mentioned, the Committee acutely feels its duty to move to make sure that we restore price stability and is determined to use its joyride to do so.</t>
         </is>
       </c>
       <c r="B604" t="n">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="C604" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D604" t="n">
         <v>1</v>
@@ -13109,11 +13109,11 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>So, you know, as I mentioned, the Committee acutely feels its duty to move to make sure that we restore price stability and is determined to use its joyride to do so.</t>
+          <t>But again, our basic forecast is one which is basically, as was pointed extinct before by Mr. Hilsenrath, a moderately optimistic forecast, where growth picks up as we pass done this period of fiscal restraint; where unemployment continues to fall at a gradual pace as it has been since last September—and we have made some procession since concluding September; and inflation rises slowly towards 2 percent.</t>
         </is>
       </c>
       <c r="B605" t="n">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="C605" t="n">
         <v>1</v>
@@ -13130,14 +13130,14 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>But again, our basic forecast is one which is basically, as was pointed extinct before by Mr. Hilsenrath, a moderately optimistic forecast, where growth picks up as we pass done this period of fiscal restraint; where unemployment continues to fall at a gradual pace as it has been since last September—and we have made some procession since concluding September; and inflation rises slowly towards 2 percent.</t>
+          <t>Of course, we can’t do anything about long-run employment opportunities, but we can help the saving recover more quickly.</t>
         </is>
       </c>
       <c r="B606" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="C606" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D606" t="n">
         <v>1</v>
@@ -13151,11 +13151,11 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>Of course, we can’t do anything about long-run employment opportunities, but we can help the saving recover more quickly.</t>
+          <t>Earlier in the year, as you will all recall, after careful study over a period of twelvemonth, actually, the Committee announced the decision to implement monetary policy in an ample-reserves authorities.</t>
         </is>
       </c>
       <c r="B607" t="n">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="C607" t="n">
         <v>0</v>
@@ -13172,7 +13172,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>Earlier in the year, as you will all recall, after careful study over a period of twelvemonth, actually, the Committee announced the decision to implement monetary policy in an ample-reserves authorities.</t>
+          <t>As you said, falling oil prices pull polish inflation.</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -13193,14 +13193,14 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>As you said, falling oil prices pull polish inflation.</t>
+          <t>If you flavor at core PCE inflation, which is a good amount of where inflation is running now, if you look at it on a 3-, 6-, and 12-month trailing annualized basis, you’ll see that inflation is at 4.8 percent, 4.5 percent, and 4.8 percent.</t>
         </is>
       </c>
       <c r="B609" t="n">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="C609" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D609" t="n">
         <v>1</v>
@@ -13214,7 +13214,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>If you flavor at core PCE inflation, which is a good amount of where inflation is running now, if you look at it on a 3-, 6-, and 12-month trailing annualized basis, you’ll see that inflation is at 4.8 percent, 4.5 percent, and 4.8 percent.</t>
+          <t>Our mandate, dingy, is price inflation.</t>
         </is>
       </c>
       <c r="B610" t="n">
@@ -13235,11 +13235,11 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>Our mandate, dingy, is price inflation.</t>
+          <t>And maybe reducing their level of the raw rate of unemployment, which has been the trend.</t>
         </is>
       </c>
       <c r="B611" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C611" t="n">
         <v>1</v>
@@ -13256,14 +13256,14 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>And maybe reducing their level of the raw rate of unemployment, which has been the trend.</t>
+          <t>The recent lower readings on inflation have been driven significantly by what appear to be one-off reduction in certain categories of prices, such as wireless telephone services and prescription drug.</t>
         </is>
       </c>
       <c r="B612" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="C612" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D612" t="n">
         <v>1</v>
@@ -13277,11 +13277,11 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>The recent lower readings on inflation have been driven significantly by what appear to be one-off reduction in certain categories of prices, such as wireless telephone services and prescription drug.</t>
+          <t>Withal, at 7.7 percent, the unemployment rate remains elevated.</t>
         </is>
       </c>
       <c r="B613" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="C613" t="n">
         <v>0</v>
@@ -13298,11 +13298,11 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>Withal, at 7.7 percent, the unemployment rate remains elevated.</t>
+          <t>I remember the—you know, in a way, the least tight aspect of it is, is looking at the unemployment rate, which is allay below our median estimate of, of [the unemployment rate consistent with] maximum employment.</t>
         </is>
       </c>
       <c r="B614" t="n">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="C614" t="n">
         <v>0</v>
@@ -13319,11 +13319,11 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>I remember the—you know, in a way, the least tight aspect of it is, is looking at the unemployment rate, which is allay below our median estimate of, of [the unemployment rate consistent with] maximum employment.</t>
+          <t>And if the stock theory of the portfolio is correct, which we trust it is, confine all of those securities off of the market and reinvesting and still keeping the, you know, rolling-over maturing securities, will still continue to put downward blackmail on interest rates.</t>
         </is>
       </c>
       <c r="B615" t="n">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="C615" t="n">
         <v>0</v>
@@ -13340,7 +13340,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>And if the stock theory of the portfolio is correct, which we trust it is, confine all of those securities off of the market and reinvesting and still keeping the, you know, rolling-over maturing securities, will still continue to put downward blackmail on interest rates.</t>
+          <t>I don’t really think asset prices themselves represent a significant threat to fiscal stability, and that’s because households are in good mold financially than they have been.</t>
         </is>
       </c>
       <c r="B616" t="n">
@@ -13361,14 +13361,14 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>I don’t really think asset prices themselves represent a significant threat to fiscal stability, and that’s because households are in good mold financially than they have been.</t>
+          <t>By contrast, raising rates too slowly would raise the risk that monetary policy would need to tighten abruptly blue the road, which could jeopardize the economic expansion.</t>
         </is>
       </c>
       <c r="B617" t="n">
-        <v>2013</v>
+        <v>2022</v>
       </c>
       <c r="C617" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D617" t="n">
         <v>1</v>
@@ -13382,14 +13382,14 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>By contrast, raising rates too slowly would raise the risk that monetary policy would need to tighten abruptly blue the road, which could jeopardize the economic expansion.</t>
+          <t>The unemployment rate declined in May and , 2020 June but, at 11.1 percent, remains far above its level before the outbreak and smashing than the Chairperson Powell’s Press Conference FINAL peak during the Planetary Financial Crisis.</t>
         </is>
       </c>
       <c r="B618" t="n">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="C618" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D618" t="n">
         <v>1</v>
@@ -13403,11 +13403,11 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>The unemployment rate declined in May and , 2020 June but, at 11.1 percent, remains far above its level before the outbreak and smashing than the Chairperson Powell’s Press Conference FINAL peak during the Planetary Financial Crisis.</t>
+          <t>So, you know, I can’t—all I can tell you is, we’ll be looking at weak world growth.</t>
         </is>
       </c>
       <c r="B619" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C619" t="n">
         <v>0</v>
@@ -13424,14 +13424,14 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>So, you know, I can’t—all I can tell you is, we’ll be looking at weak world growth.</t>
+          <t>I think we all agree that the economy is pee progress, that we are tightlipped to an unemployment rate that is one that’s sustainable in the longer run.</t>
         </is>
       </c>
       <c r="B620" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="C620" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D620" t="n">
         <v>1</v>
@@ -13445,11 +13445,11 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>I think we all agree that the economy is pee progress, that we are tightlipped to an unemployment rate that is one that’s sustainable in the longer run.</t>
+          <t>In addition, the May 1, 2019 trimmed mean measures of inflation did not go downwardly as much.</t>
         </is>
       </c>
       <c r="B621" t="n">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="C621" t="n">
         <v>1</v>
@@ -13466,14 +13466,14 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>In addition, the May 1, 2019 trimmed mean measures of inflation did not go downwardly as much.</t>
+          <t>Well, we—as a Committee, we do not want inflation undershoots.</t>
         </is>
       </c>
       <c r="B622" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C622" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D622" t="n">
         <v>1</v>
@@ -13487,11 +13487,11 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>Well, we—as a Committee, we do not want inflation undershoots.</t>
+          <t>By getting unemployment down, we hope to bring back to work some of the mass who’ve been out of work as long as they have and, in that respect, adjudicate to avoid the longer-term consequences of mass being out of work for months at a time.</t>
         </is>
       </c>
       <c r="B623" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C623" t="n">
         <v>0</v>
@@ -13508,11 +13508,11 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>By getting unemployment down, we hope to bring back to work some of the mass who’ve been out of work as long as they have and, in that respect, adjudicate to avoid the longer-term consequences of mass being out of work for months at a time.</t>
+          <t>Inflation has continued to run below our longer-run objective, in part reflecting lower push prices.</t>
         </is>
       </c>
       <c r="B624" t="n">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="C624" t="n">
         <v>0</v>
@@ -13529,11 +13529,11 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>Inflation has continued to run below our longer-run objective, in part reflecting lower push prices.</t>
+          <t>During this time of reopening, we are likely to see some upward pressure on prices, and I’ll discus why.</t>
         </is>
       </c>
       <c r="B625" t="n">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="C625" t="n">
         <v>0</v>
@@ -13550,7 +13550,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>During this time of reopening, we are likely to see some upward pressure on prices, and I’ll discus why.</t>
+          <t>When we reach maximum employment, when we reach a commonwealth where labor mart conditions are at maximum employment in the Committee’s judgment, it’s very possible that the inflation test will already be met.</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -13571,14 +13571,14 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>When we reach maximum employment, when we reach a commonwealth where labor mart conditions are at maximum employment in the Committee’s judgment, it’s very possible that the inflation test will already be met.</t>
+          <t>And—but inflation anticipation did not move strongly down here in the United States.</t>
         </is>
       </c>
       <c r="B627" t="n">
-        <v>2017</v>
+        <v>2011</v>
       </c>
       <c r="C627" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D627" t="n">
         <v>1</v>
@@ -13592,14 +13592,14 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>And—but inflation anticipation did not move strongly down here in the United States.</t>
+          <t>Easily, if the economy worsens and inflation continue relatively low, then we wouldn’t begin to exit, and, therefore, we wouldn’t change the language.</t>
         </is>
       </c>
       <c r="B628" t="n">
-        <v>2011</v>
+        <v>2020</v>
       </c>
       <c r="C628" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D628" t="n">
         <v>1</v>
@@ -13613,14 +13613,14 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>Easily, if the economy worsens and inflation continue relatively low, then we wouldn’t begin to exit, and, therefore, we wouldn’t change the language.</t>
+          <t>The American economy is very strong and good positioned to handle tighter monetary policy.</t>
         </is>
       </c>
       <c r="B629" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C629" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D629" t="n">
         <v>1</v>
@@ -13634,14 +13634,14 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>The American economy is very strong and good positioned to handle tighter monetary policy.</t>
+          <t>And inflation is moving—move up, I think, toward our 2 percent objective.</t>
         </is>
       </c>
       <c r="B630" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="C630" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D630" t="n">
         <v>1</v>
@@ -13655,11 +13655,11 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>And inflation is moving—move up, I think, toward our 2 percent objective.</t>
+          <t>We have a 2 percentage symmetric inflation objective, and, for a number of years now, inflation has been running under 2 percent.</t>
         </is>
       </c>
       <c r="B631" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="C631" t="n">
         <v>0</v>
@@ -13676,11 +13676,11 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>We have a 2 percentage symmetric inflation objective, and, for a number of years now, inflation has been running under 2 percent.</t>
+          <t>And what we—it looks like we’re seeing a retardation in the rate of growth.</t>
         </is>
       </c>
       <c r="B632" t="n">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="C632" t="n">
         <v>0</v>
@@ -13697,11 +13697,11 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>And what we—it looks like we’re seeing a retardation in the rate of growth.</t>
+          <t>And no, we’re not—we, we have not at all changed our view, and I haven’t changed my view that inflation go above 2 percent, moderately above 2 percentage, is a desirable thing.</t>
         </is>
       </c>
       <c r="B633" t="n">
-        <v>2022</v>
+        <v>2011</v>
       </c>
       <c r="C633" t="n">
         <v>0</v>
@@ -13718,35 +13718,35 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>And no, we’re not—we, we have not at all changed our view, and I haven’t changed my view that inflation go above 2 percent, moderately above 2 percentage, is a desirable thing.</t>
+          <t>One of the things we’ve learned from our financial crisis and from a series of financial crises [MASK] [MASK] [MASK] [MASK] the globe [MASK] that, very [MASK], when the economy [MASK] [MASK] hit and falls into a recession, that productivity doesn’t pick [MASK] [MASK] pre-recession levels and that [MASK] looks like there is a permanent hit [MASK] the path of potential output for the economy, which is [MASK] “hysteresis.” And I raised the question as [MASK] whether or not this might operate in the opposite direction as well.</t>
         </is>
       </c>
       <c r="B634" t="n">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="C634" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D634" t="n">
         <v>1</v>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>synonym_replacement</t>
+          <t>masking</t>
         </is>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>One of the things we’ve learned from our financial crisis and from a series of financial crises [MASK] [MASK] [MASK] [MASK] the globe [MASK] that, very [MASK], when the economy [MASK] [MASK] hit and falls into a recession, that productivity doesn’t pick [MASK] [MASK] pre-recession levels and that [MASK] looks like there is a permanent hit [MASK] the path of potential output for the economy, which is [MASK] “hysteresis.” And I raised the question as [MASK] whether or not this might operate in the opposite direction as well.</t>
+          <t>It was a question of not getting inflation up to our target on a [MASK], symmetric kind [MASK] a [MASK].</t>
         </is>
       </c>
       <c r="B635" t="n">
         <v>2021</v>
       </c>
       <c r="C635" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D635" t="n">
         <v>1</v>
@@ -13760,14 +13760,14 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>It was a question of not getting inflation up to our target on a [MASK], symmetric kind [MASK] a [MASK].</t>
+          <t>We have long [MASK] that the size of the balance sheet will be considered normalized when the balance [MASK] [MASK] once again at [MASK] smallest level consistent with [MASK] monetary policy efficiently and effectively.</t>
         </is>
       </c>
       <c r="B636" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C636" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D636" t="n">
         <v>1</v>
@@ -13781,11 +13781,11 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>We have long [MASK] that the size of the balance sheet will be considered normalized when the balance [MASK] [MASK] once again at [MASK] smallest level consistent with [MASK] monetary policy efficiently and effectively.</t>
+          <t>As a further step in enhancing the clarity of our [MASK], the Committee recently decided to begin publishing information about [MASK]’ assessments of [MASK] [MASK] policy—that [MASK], the path of policy that each [MASK] [MASK] as most [MASK] to foster mandate-consistent outcomes for employment and inflation if the economy evolves as expected.</t>
         </is>
       </c>
       <c r="B637" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C637" t="n">
         <v>2</v>
@@ -13802,11 +13802,11 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>As a further step in enhancing the clarity of our [MASK], the Committee recently decided to begin publishing information about [MASK]’ assessments of [MASK] [MASK] policy—that [MASK], the path of policy that each [MASK] [MASK] as most [MASK] to foster mandate-consistent outcomes for employment and inflation if the economy evolves as expected.</t>
+          <t>That means [MASK] we can run at low levels [MASK] unemployment and [MASK] a historically good—in some dimensions—labor market without having [MASK] worry about inflation.</t>
         </is>
       </c>
       <c r="B638" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C638" t="n">
         <v>2</v>
@@ -13823,11 +13823,11 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>That means [MASK] we can run at low levels [MASK] unemployment and [MASK] a historically good—in some dimensions—labor market without having [MASK] worry about inflation.</t>
+          <t>Looking ahead, FOMC participants project [MASK] unemployment rate to continue to decline; the median projection [MASK] 5 percent at the [MASK] of next year and moves below 4 percent [MASK] 2023.</t>
         </is>
       </c>
       <c r="B639" t="n">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C639" t="n">
         <v>2</v>
@@ -13844,14 +13844,14 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>Looking ahead, FOMC participants project [MASK] unemployment rate to continue to decline; the median projection [MASK] 5 percent at the [MASK] of next year and moves below 4 percent [MASK] 2023.</t>
+          <t>I [MASK]’t really think asset prices themselves represent a significant threat to financial stability, and that’s [MASK] households are [MASK] good shape financially [MASK] they have been.</t>
         </is>
       </c>
       <c r="B640" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="C640" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D640" t="n">
         <v>1</v>
@@ -13865,14 +13865,14 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>I [MASK]’t really think asset prices themselves represent a significant threat to financial stability, and that’s [MASK] households are [MASK] good shape financially [MASK] they have been.</t>
+          <t>I would say, in the area of commercial [MASK] estate, while valuations are high, we [MASK] seeing some tightening [MASK] lending standards and [MASK] debt growth associated with [MASK] rise in commercial real estate prices.</t>
         </is>
       </c>
       <c r="B641" t="n">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="C641" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D641" t="n">
         <v>1</v>
@@ -13886,14 +13886,14 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>I would say, in the area of commercial [MASK] estate, while valuations are high, we [MASK] seeing some tightening [MASK] lending standards and [MASK] debt growth associated with [MASK] rise in commercial real estate prices.</t>
+          <t>It isn’t really just targeting the headline [MASK], but [MASK]’s about taking all of [MASK] things into [MASK] in your thinking about what constitutes maximum employment.</t>
         </is>
       </c>
       <c r="B642" t="n">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="C642" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D642" t="n">
         <v>1</v>
@@ -13907,14 +13907,14 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>It isn’t really just targeting the headline [MASK], but [MASK]’s about taking all of [MASK] things into [MASK] in your thinking about what constitutes maximum employment.</t>
+          <t>[MASK] we reach maximum employment, when we reach a state where labor [MASK] conditions are at [MASK] [MASK] in the Committee’s [MASK], it’s very possible that the inflation test will already be met.</t>
         </is>
       </c>
       <c r="B643" t="n">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="C643" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D643" t="n">
         <v>1</v>
@@ -13928,14 +13928,14 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>[MASK] we reach maximum employment, when we reach a state where labor [MASK] conditions are at [MASK] [MASK] in the Committee’s [MASK], it’s very possible that the inflation test will already be met.</t>
+          <t>So you’re talking about the inflation target, [MASK].</t>
         </is>
       </c>
       <c r="B644" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="C644" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D644" t="n">
         <v>1</v>
@@ -13949,14 +13949,14 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>So you’re talking about the inflation target, [MASK].</t>
+          <t>Well, you know, [MASK] the economy were disappointing, we—you know, our actions wouldn’t purely [MASK] [MASK] on inflation, we would also take employment [MASK] account.</t>
         </is>
       </c>
       <c r="B645" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C645" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D645" t="n">
         <v>1</v>
@@ -13970,14 +13970,14 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>Well, you know, [MASK] the economy were disappointing, we—you know, our actions wouldn’t purely [MASK] [MASK] on inflation, we would also take employment [MASK] account.</t>
+          <t>So you’re [MASK], you’re seeing—I, I can’t remember the number, [MASK] [MASK] might [MASK] in the 3s—3, 3½ percent growth for next year.</t>
         </is>
       </c>
       <c r="B646" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C646" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D646" t="n">
         <v>1</v>
@@ -13991,11 +13991,11 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>So you’re [MASK], you’re seeing—I, I can’t remember the number, [MASK] [MASK] might [MASK] in the 3s—3, 3½ percent growth for next year.</t>
+          <t>We have not seen wage [MASK] pick up.</t>
         </is>
       </c>
       <c r="B647" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C647" t="n">
         <v>2</v>
@@ -14012,7 +14012,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>We have not seen wage [MASK] pick up.</t>
+          <t>And so what that means [MASK] the Federal Reserve cannot [MASK] monetary accommodation by [MASK] short-term interest rates, the usual approach.</t>
         </is>
       </c>
       <c r="B648" t="n">
@@ -14033,7 +14033,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>And so what that means [MASK] the Federal Reserve cannot [MASK] monetary accommodation by [MASK] short-term interest rates, the usual approach.</t>
+          <t>[MASK] have a three-part baseline projection, which [MASK] increasing growth that’s picking up over time as fiscal [MASK] is reduced, continuing gains in [MASK] labor [MASK], and inflation moving back towards objective.</t>
         </is>
       </c>
       <c r="B649" t="n">
@@ -14054,14 +14054,14 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>[MASK] have a three-part baseline projection, which [MASK] increasing growth that’s picking up over time as fiscal [MASK] is reduced, continuing gains in [MASK] labor [MASK], and inflation moving back towards objective.</t>
+          <t>So on the first, the [MASK]’s forecasts and those of most [MASK] forecasters do show growth running below [MASK] longer-run [MASK] this year and next year.</t>
         </is>
       </c>
       <c r="B650" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C650" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D650" t="n">
         <v>1</v>
@@ -14075,14 +14075,14 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>So on the first, the [MASK]’s forecasts and those of most [MASK] forecasters do show growth running below [MASK] longer-run [MASK] this year and next year.</t>
+          <t>[MASK] would further say that I think it’s important to [MASK] that we’re not [MASK] to mechanically take the interest rate projections that [MASK] provide [MASK] just build policy off of that.</t>
         </is>
       </c>
       <c r="B651" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C651" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D651" t="n">
         <v>1</v>
@@ -14096,7 +14096,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>[MASK] would further say that I think it’s important to [MASK] that we’re not [MASK] to mechanically take the interest rate projections that [MASK] provide [MASK] just build policy off of that.</t>
+          <t>So in [MASK] of financial markets and monetary policy, we—as we say in our statement every cycle, we do take financial conditions into consideration because financial—broader [MASK] conditions do affect the broader [MASK], and they’[MASK] one of the [MASK] things that [MASK] [MASK] into account.</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -14117,14 +14117,14 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>So in [MASK] of financial markets and monetary policy, we—as we say in our statement every cycle, we do take financial conditions into consideration because financial—broader [MASK] conditions do affect the broader [MASK], and they’[MASK] one of the [MASK] things that [MASK] [MASK] into account.</t>
+          <t>But in many [MASK] around the Chair Yellen’s [MASK] Conference FINAL world that are important commodity exporters, the [MASK] [MASK]’ve seen in oil prices has had a depressing effect on their growth, their trade with us [MASK] [MASK] trade partners, and caused problems [MASK] have had spillovers [MASK] the global economy as well.</t>
         </is>
       </c>
       <c r="B653" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="C653" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D653" t="n">
         <v>1</v>
@@ -14138,11 +14138,11 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>But in many [MASK] around the Chair Yellen’s [MASK] Conference FINAL world that are important commodity exporters, the [MASK] [MASK]’ve seen in oil prices has had a depressing effect on their growth, their trade with us [MASK] [MASK] trade partners, and caused problems [MASK] have had spillovers [MASK] the global economy as well.</t>
+          <t>More broadly, however, weaker demand, especially in sectors that [MASK] been most affected by [MASK] pandemic, has [MASK] down consumer prices, and [MASK], inflation is running well [MASK] our 2 percent longer-run objective.</t>
         </is>
       </c>
       <c r="B654" t="n">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="C654" t="n">
         <v>0</v>
@@ -14159,14 +14159,14 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>More broadly, however, weaker demand, especially in sectors that [MASK] been most affected by [MASK] pandemic, has [MASK] down consumer prices, and [MASK], inflation is running well [MASK] our 2 percent longer-run objective.</t>
+          <t>[MASK] was to do with, you know, strong monetary policy and [MASK] stimulus into an economy that was recovering [MASK], and in which there were [MASK] supply-side barriers which effectively [MASK] to, you know, in certain [MASK] of the economy, what you might call a [MASK] supply curve.</t>
         </is>
       </c>
       <c r="B655" t="n">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="C655" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D655" t="n">
         <v>1</v>
@@ -14180,14 +14180,14 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>[MASK] was to do with, you know, strong monetary policy and [MASK] stimulus into an economy that was recovering [MASK], and in which there were [MASK] supply-side barriers which effectively [MASK] to, you know, in certain [MASK] of the economy, what you might call a [MASK] supply curve.</t>
+          <t>And then, what the [MASK] [MASK], [MASK] this is the same language we used in December and [MASK], we used the language especially if inflation is [MASK] below our 2 percent objective.</t>
         </is>
       </c>
       <c r="B656" t="n">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="C656" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D656" t="n">
         <v>1</v>
@@ -14201,14 +14201,14 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>And then, what the [MASK] [MASK], [MASK] this is the same language we used in December and [MASK], we used the language especially if inflation is [MASK] below our 2 percent objective.</t>
+          <t>We are hopeful that Europe will take additional measures and [MASK] all that’s necessary to stabilize the situation and to provide the basis for an ongoing stable [MASK] [MASK]—in which [MASK] and [MASK] are both stabilized, in which there’s [MASK] program for growth, and in which fiscal arrangements [MASK] [MASK]—are made much [MASK].</t>
         </is>
       </c>
       <c r="B657" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="C657" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D657" t="n">
         <v>1</v>
@@ -14222,11 +14222,11 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>We are hopeful that Europe will take additional measures and [MASK] all that’s necessary to stabilize the situation and to provide the basis for an ongoing stable [MASK] [MASK]—in which [MASK] and [MASK] are both stabilized, in which there’s [MASK] program for growth, and in which fiscal arrangements [MASK] [MASK]—are made much [MASK].</t>
+          <t>So, we are taking account of [MASK] developments, including prospects for growth in our [MASK] partners, [MASK] making the forecast we have here.</t>
         </is>
       </c>
       <c r="B658" t="n">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="C658" t="n">
         <v>2</v>
@@ -14243,11 +14243,11 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>So, we are taking account of [MASK] developments, including prospects for growth in our [MASK] partners, [MASK] making the forecast we have here.</t>
+          <t>Again, while I do not shirk the responsibility of [MASK] Fed having to do what it can to meet its [MASK], obviously, a broad range [MASK] policies can [MASK] growth and employment, [MASK] I hope that [MASK] will be a range of actions that will complement and supplement [MASK] Federal [MASK]’s efforts.</t>
         </is>
       </c>
       <c r="B659" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="C659" t="n">
         <v>2</v>
@@ -14264,14 +14264,14 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>Again, while I do not shirk the responsibility of [MASK] Fed having to do what it can to meet its [MASK], obviously, a broad range [MASK] policies can [MASK] growth and employment, [MASK] I hope that [MASK] will be a range of actions that will complement and supplement [MASK] Federal [MASK]’s efforts.</t>
+          <t>Business and household spending are increasing at rates [MASK] with moderate [MASK] growth, [MASK] [MASK] spending appears to be rising at a somewhat slower pace than earlier this year.</t>
         </is>
       </c>
       <c r="B660" t="n">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="C660" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D660" t="n">
         <v>1</v>
@@ -14285,11 +14285,11 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>Business and household spending are increasing at rates [MASK] with moderate [MASK] growth, [MASK] [MASK] spending appears to be rising at a somewhat slower pace than earlier this year.</t>
+          <t>If you look at the number of job openings compared to [MASK] [MASK] of unemployed, [MASK]’s—we’re, we’re clearly on a path to a very strong labor market with high participation, low unemployment, high employment, [MASK] moving up [MASK] [MASK] [MASK].</t>
         </is>
       </c>
       <c r="B661" t="n">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="C661" t="n">
         <v>1</v>
@@ -14306,14 +14306,14 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>If you look at the number of job openings compared to [MASK] [MASK] of unemployed, [MASK]’s—we’re, we’re clearly on a path to a very strong labor market with high participation, low unemployment, high employment, [MASK] moving up [MASK] [MASK] [MASK].</t>
+          <t>What I’m [MASK] you is that the stance of monetary [MASK] we have [MASK], we believe, is appropriate.</t>
         </is>
       </c>
       <c r="B662" t="n">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="C662" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D662" t="n">
         <v>1</v>
@@ -14327,14 +14327,14 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>What I’m [MASK] you is that the stance of monetary [MASK] we have [MASK], we believe, is appropriate.</t>
+          <t>As [MASK], our [MASK] are guided by [MASK] congressional mandate to promote maximum employment and price stability.</t>
         </is>
       </c>
       <c r="B663" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C663" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D663" t="n">
         <v>1</v>
@@ -14348,14 +14348,14 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>As [MASK], our [MASK] are guided by [MASK] congressional mandate to promote maximum employment and price stability.</t>
+          <t>Our tools work [MASK] demand.</t>
         </is>
       </c>
       <c r="B664" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="C664" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D664" t="n">
         <v>1</v>
@@ -14369,14 +14369,14 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>Our tools work [MASK] demand.</t>
+          <t>The recent [MASK] readings on inflation have been driven significantly by what appear [MASK] be one-off reductions in certain categories of [MASK], such [MASK] [MASK] telephone services and prescription drugs.</t>
         </is>
       </c>
       <c r="B665" t="n">
         <v>2012</v>
       </c>
       <c r="C665" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D665" t="n">
         <v>1</v>
@@ -14390,14 +14390,14 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>The recent [MASK] readings on inflation have been driven significantly by what appear [MASK] be one-off reductions in certain categories of [MASK], such [MASK] [MASK] telephone services and prescription drugs.</t>
+          <t>Of course, we’re ready [MASK] provide [MASK] that Congress needs to evaluate the Fed’s decisionmaking, in monetary policy and [MASK].</t>
         </is>
       </c>
       <c r="B666" t="n">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="C666" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D666" t="n">
         <v>1</v>
@@ -14411,14 +14411,14 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>Of course, we’re ready [MASK] provide [MASK] that Congress needs to evaluate the Fed’s decisionmaking, in monetary policy and [MASK].</t>
+          <t>The shock that the—[MASK] the pandemic was unprecedented both [MASK] its nature and in its size and [MASK] the amount of unemployment [MASK] [MASK] created and in the shock to economic activity.</t>
         </is>
       </c>
       <c r="B667" t="n">
-        <v>2021</v>
+        <v>2012</v>
       </c>
       <c r="C667" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D667" t="n">
         <v>1</v>
@@ -14432,14 +14432,14 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>The shock that the—[MASK] the pandemic was unprecedented both [MASK] its nature and in its size and [MASK] the amount of unemployment [MASK] [MASK] created and in the shock to economic activity.</t>
+          <t>I would describe [MASK] [MASK] of wage growth as having moved up some.</t>
         </is>
       </c>
       <c r="B668" t="n">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="C668" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D668" t="n">
         <v>1</v>
@@ -14453,11 +14453,11 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>I would describe [MASK] [MASK] of wage growth as having moved up some.</t>
+          <t>So the—the sooner we [MASK] the virus under control, the sooner people can [MASK] that confidence and regain their [MASK] activity.</t>
         </is>
       </c>
       <c r="B669" t="n">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="C669" t="n">
         <v>2</v>
@@ -14474,14 +14474,14 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>So the—the sooner we [MASK] the virus under control, the sooner people can [MASK] that confidence and regain their [MASK] activity.</t>
+          <t>And we were actually [MASK] concerned that growth [MASK] not sufficient to continue to bring the [MASK] rate down.</t>
         </is>
       </c>
       <c r="B670" t="n">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="C670" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D670" t="n">
         <v>1</v>
@@ -14495,7 +14495,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>And we were actually [MASK] concerned that growth [MASK] not sufficient to continue to bring the [MASK] rate down.</t>
+          <t>As you said, falling oil [MASK] pull down inflation.</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -14516,14 +14516,14 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>As you said, falling oil [MASK] pull down inflation.</t>
+          <t>But, certainly, we’ve had a lot of [MASK] in which interest rates have [MASK] low.</t>
         </is>
       </c>
       <c r="B672" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="C672" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D672" t="n">
         <v>1</v>
@@ -14537,11 +14537,11 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>But, certainly, we’ve had a lot of [MASK] in which interest rates have [MASK] low.</t>
+          <t>Returning [MASK] monetary [MASK], we recognize that there has been a great deal of focus on today’[MASK] policy decision.</t>
         </is>
       </c>
       <c r="B673" t="n">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="C673" t="n">
         <v>2</v>
@@ -14558,11 +14558,11 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>Returning [MASK] monetary [MASK], we recognize that there has been a great deal of focus on today’[MASK] policy decision.</t>
+          <t>So and, and, you know, the shorter-term ones [MASK] tend to move [MASK] based on, for [MASK], gasoline prices.</t>
         </is>
       </c>
       <c r="B674" t="n">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="C674" t="n">
         <v>2</v>
@@ -14579,14 +14579,14 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>So and, and, you know, the shorter-term ones [MASK] tend to move [MASK] based on, for [MASK], gasoline prices.</t>
+          <t>We want to [MASK] lower unemployment.</t>
         </is>
       </c>
       <c r="B675" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C675" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D675" t="n">
         <v>1</v>
@@ -14600,11 +14600,11 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>We want to [MASK] lower unemployment.</t>
+          <t>[MASK] for [MASK], many years, we’ve been far from maximum employment and stable prices, and so the need for accommodative policy [MASK] been—has been [MASK].</t>
         </is>
       </c>
       <c r="B676" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C676" t="n">
         <v>0</v>
@@ -14621,14 +14621,14 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>[MASK] for [MASK], many years, we’ve been far from maximum employment and stable prices, and so the need for accommodative policy [MASK] been—has been [MASK].</t>
+          <t>Wage [MASK] has been running at 2 percent.</t>
         </is>
       </c>
       <c r="B677" t="n">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="C677" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D677" t="n">
         <v>1</v>
@@ -14642,14 +14642,14 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>Wage [MASK] has been running at 2 percent.</t>
+          <t>As [MASK] [MASK] by the Bureau of Labor Statistics, this figure [MASK] understates the extent of unemployment; accounting for the unusually large number of workers who reported themselves [MASK] employed but absent from their jobs would [MASK] the unemployment [MASK] by about 3 percentage [MASK].</t>
         </is>
       </c>
       <c r="B678" t="n">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="C678" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D678" t="n">
         <v>1</v>
@@ -14663,14 +14663,14 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>As [MASK] [MASK] by the Bureau of Labor Statistics, this figure [MASK] understates the extent of unemployment; accounting for the unusually large number of workers who reported themselves [MASK] employed but absent from their jobs would [MASK] the unemployment [MASK] by about 3 percentage [MASK].</t>
+          <t>[MASK] are, [MASK] know, this is—this is the economy at nearly full employment [MASK] in the range—in [MASK] neighborhood of full employment.</t>
         </is>
       </c>
       <c r="B679" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="C679" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D679" t="n">
         <v>1</v>
@@ -14684,14 +14684,14 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>[MASK] are, [MASK] know, this is—this is the economy at nearly full employment [MASK] in the range—in [MASK] neighborhood of full employment.</t>
+          <t>If inflation [MASK] [MASK] during the course of 2022, then we may already have met that test by the [MASK] we reach liftoff.</t>
         </is>
       </c>
       <c r="B680" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C680" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D680" t="n">
         <v>1</v>
@@ -14705,14 +14705,14 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>If inflation [MASK] [MASK] during the course of 2022, then we may already have met that test by the [MASK] we reach liftoff.</t>
+          <t>The [MASK] Reserve’s [MASK] is [MASK] by our mandate to promote maximum employment and stable prices for the American people, along with [MASK] responsibilities to promote the [MASK] of the financial system.</t>
         </is>
       </c>
       <c r="B681" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="C681" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D681" t="n">
         <v>1</v>
@@ -14726,11 +14726,11 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>The [MASK] Reserve’s [MASK] is [MASK] by our mandate to promote maximum employment and stable prices for the American people, along with [MASK] responsibilities to promote the [MASK] of the financial system.</t>
+          <t>Our [MASK], sorry, is price inflation.</t>
         </is>
       </c>
       <c r="B682" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C682" t="n">
         <v>1</v>
@@ -14747,14 +14747,14 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>Our [MASK], sorry, is price inflation.</t>
+          <t>These base effects will contribute about 1 [MASK] point to headline inflation and about 0.7 percentage point [MASK] core inflation in April [MASK] May.</t>
         </is>
       </c>
       <c r="B683" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C683" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D683" t="n">
         <v>1</v>
@@ -14768,11 +14768,11 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>These base effects will contribute about 1 [MASK] point to headline inflation and about 0.7 percentage point [MASK] core inflation in April [MASK] May.</t>
+          <t>[MASK] [MASK]’s not easy to get a clear read on the implications of asset prices [MASK] the overall outlook.</t>
         </is>
       </c>
       <c r="B684" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C684" t="n">
         <v>2</v>
@@ -14789,7 +14789,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>[MASK] [MASK]’s not easy to get a clear read on the implications of asset prices [MASK] the overall outlook.</t>
+          <t>The Phillips [MASK] [MASK] become, according to most estimates, [MASK] flat in the sense that movements in [MASK] have only a modest impact on [MASK], so we shouldn’t overblow how large that is.</t>
         </is>
       </c>
       <c r="B685" t="n">
@@ -14810,7 +14810,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>The Phillips [MASK] [MASK] become, according to most estimates, [MASK] flat in the sense that movements in [MASK] have only a modest impact on [MASK], so we shouldn’t overblow how large that is.</t>
+          <t>We [MASK] don’t conduct monetary policy in order to prove our [MASK].</t>
         </is>
       </c>
       <c r="B686" t="n">
@@ -14831,11 +14831,11 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>We [MASK] don’t conduct monetary policy in order to prove our [MASK].</t>
+          <t>It [MASK] not [MASK] Taylor rule but [MASK] has the [MASK] feature that it relates policy to observables in the economy, such as unemployment and inflation.</t>
         </is>
       </c>
       <c r="B687" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C687" t="n">
         <v>2</v>
@@ -14852,11 +14852,11 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>It [MASK] not [MASK] Taylor rule but [MASK] has the [MASK] feature that it relates policy to observables in the economy, such as unemployment and inflation.</t>
+          <t>Smoothing through these [MASK], average monthly job growth appears to have stepped down from [MASK] [MASK]’s strong pace, but job gains remain well above the pace necessary [MASK] provide jobs for new labor [MASK] entrants.</t>
         </is>
       </c>
       <c r="B688" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C688" t="n">
         <v>2</v>
@@ -14873,11 +14873,11 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>Smoothing through these [MASK], average monthly job growth appears to have stepped down from [MASK] [MASK]’s strong pace, but job gains remain well above the pace necessary [MASK] provide jobs for new labor [MASK] entrants.</t>
+          <t>It also [MASK] stock prices.</t>
         </is>
       </c>
       <c r="B689" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C689" t="n">
         <v>2</v>
@@ -14894,14 +14894,14 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>It also [MASK] stock prices.</t>
+          <t>Inflation has [MASK] up in recent [MASK], mainly reflecting higher prices [MASK] some commodities and imported goods.</t>
         </is>
       </c>
       <c r="B690" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="C690" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D690" t="n">
         <v>1</v>
@@ -14915,14 +14915,14 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>Inflation has [MASK] up in recent [MASK], mainly reflecting higher prices [MASK] some commodities and imported goods.</t>
+          <t>The second point that I made was that when short-term interest rates hit zero, the tools of a [MASK] bank are no [MASK]—[MASK] not exhausted, there are still [MASK] things that the central bank can do to [MASK] additional [MASK].</t>
         </is>
       </c>
       <c r="B691" t="n">
         <v>2012</v>
       </c>
       <c r="C691" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D691" t="n">
         <v>1</v>
@@ -14936,14 +14936,14 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>The second point that I made was that when short-term interest rates hit zero, the tools of a [MASK] bank are no [MASK]—[MASK] not exhausted, there are still [MASK] things that the central bank can do to [MASK] additional [MASK].</t>
+          <t>In spite of having such slow [MASK], disappointing [MASK] growth, we have [MASK] labor market that last year [MASK] an average [MASK] about 230,000 jobs a month and so far this year has been generating about 180,000 [MASK] a month.</t>
         </is>
       </c>
       <c r="B692" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="C692" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D692" t="n">
         <v>1</v>
@@ -14957,14 +14957,14 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>In spite of having such slow [MASK], disappointing [MASK] growth, we have [MASK] labor market that last year [MASK] an average [MASK] about 230,000 jobs a month and so far this year has been generating about 180,000 [MASK] a month.</t>
+          <t>So I think, through all [MASK] those channels, monetary [MASK] works.</t>
         </is>
       </c>
       <c r="B693" t="n">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="C693" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D693" t="n">
         <v>1</v>
@@ -14978,11 +14978,11 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>So I think, through all [MASK] those channels, monetary [MASK] works.</t>
+          <t>As [MASK], each participant’[MASK] [MASK] are conditioned on his or her own view of appropriate monetary policy.</t>
         </is>
       </c>
       <c r="B694" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C694" t="n">
         <v>2</v>
@@ -14999,14 +14999,14 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>As [MASK], each participant’[MASK] [MASK] are conditioned on his or her own view of appropriate monetary policy.</t>
+          <t>And productivity’s been [MASK] low.</t>
         </is>
       </c>
       <c r="B695" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C695" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D695" t="n">
         <v>1</v>
@@ -15020,14 +15020,14 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>And productivity’s been [MASK] low.</t>
+          <t>But again, [MASK] terms of terminology, I [MASK] I would reject that term for the Federal [MASK] because we [MASK] going to be evenhanded in treating the [MASK] stability and maximum employment parts of our mandate [MASK] a level footing.</t>
         </is>
       </c>
       <c r="B696" t="n">
-        <v>2020</v>
+        <v>2011</v>
       </c>
       <c r="C696" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D696" t="n">
         <v>1</v>
@@ -15041,11 +15041,11 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>But again, [MASK] terms of terminology, I [MASK] I would reject that term for the Federal [MASK] because we [MASK] going to be evenhanded in treating the [MASK] stability and maximum employment parts of our mandate [MASK] a level footing.</t>
+          <t>[MASK] is a positive for growth.</t>
         </is>
       </c>
       <c r="B697" t="n">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="C697" t="n">
         <v>2</v>
@@ -15062,14 +15062,14 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>[MASK] is a positive for growth.</t>
+          <t>And [MASK] [MASK] stock theory [MASK] the portfolio is correct, which we [MASK] it is, holding all of those securities off of the [MASK] and reinvesting and still keeping the, you know, rolling-over [MASK] securities, will still continue to [MASK] downward pressure on interest rates.</t>
         </is>
       </c>
       <c r="B698" t="n">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="C698" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D698" t="n">
         <v>1</v>
@@ -15083,11 +15083,11 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>And [MASK] [MASK] stock theory [MASK] the portfolio is correct, which we [MASK] it is, holding all of those securities off of the [MASK] and reinvesting and still keeping the, you know, rolling-over [MASK] securities, will still continue to [MASK] downward pressure on interest rates.</t>
+          <t>And you know, [MASK] haven’t yet—we [MASK] touched 2 percent core inflation, to pick one measure—just touched it for a few months, and then [MASK]’ve [MASK] back.</t>
         </is>
       </c>
       <c r="B699" t="n">
-        <v>2013</v>
+        <v>2022</v>
       </c>
       <c r="C699" t="n">
         <v>0</v>
@@ -15104,14 +15104,14 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>And you know, [MASK] haven’t yet—we [MASK] touched 2 percent core inflation, to pick one measure—just touched it for a few months, and then [MASK]’ve [MASK] back.</t>
+          <t>[MASK] we’re learning to, to engage [MASK] economic activity.</t>
         </is>
       </c>
       <c r="B700" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C700" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D700" t="n">
         <v>1</v>
@@ -15125,14 +15125,14 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>[MASK] we’re learning to, to engage [MASK] economic activity.</t>
+          <t>[MASK] Federal Reserve is fully committed [MASK] [MASK] sides of its mandate—to price stability as [MASK] as to maximum employment—and it [MASK] both the [MASK] and the will to act at the appropriate time to avoid any emerging threat to [MASK] stability.</t>
         </is>
       </c>
       <c r="B701" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="C701" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D701" t="n">
         <v>1</v>
@@ -15146,14 +15146,14 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>[MASK] Federal Reserve is fully committed [MASK] [MASK] sides of its mandate—to price stability as [MASK] as to maximum employment—and it [MASK] both the [MASK] and the will to act at the appropriate time to avoid any emerging threat to [MASK] stability.</t>
+          <t>We have [MASK] focused on whether we meet [MASK] liftoff test, because we [MASK]’t meet the liftoff test now because we’[MASK] not at maximum employment.</t>
         </is>
       </c>
       <c r="B702" t="n">
         <v>2020</v>
       </c>
       <c r="C702" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D702" t="n">
         <v>1</v>
@@ -15167,14 +15167,14 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>We have [MASK] focused on whether we meet [MASK] liftoff test, because we [MASK]’t meet the liftoff test now because we’[MASK] not at maximum employment.</t>
+          <t>For example, one—[MASK] the [MASK]-run, the size of the balance sheet is going to depend on the [MASK]’s demand for our liabilities, including currency [MASK] reserves.</t>
         </is>
       </c>
       <c r="B703" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C703" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D703" t="n">
         <v>1</v>
@@ -15188,14 +15188,14 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>For example, one—[MASK] the [MASK]-run, the size of the balance sheet is going to depend on the [MASK]’s demand for our liabilities, including currency [MASK] reserves.</t>
+          <t>So, there has been impact through lower [MASK] rates, but I think more broadly is [MASK] indirect [MASK].</t>
         </is>
       </c>
       <c r="B704" t="n">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="C704" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D704" t="n">
         <v>1</v>
@@ -15209,14 +15209,14 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>So, there has been impact through lower [MASK] rates, but I think more broadly is [MASK] indirect [MASK].</t>
+          <t>We're looking at wages and we're looking [MASK] [MASK] inflation.</t>
         </is>
       </c>
       <c r="B705" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="C705" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D705" t="n">
         <v>1</v>
@@ -15230,11 +15230,11 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>We're looking at wages and we're looking [MASK] [MASK] inflation.</t>
+          <t>I’[MASK] [MASK] saying, that, that is [MASK] fiscal policy can [MASK] that, really, monetary policy can’t do—is, is invest in the future productive capacity of [MASK] economy, raise potential growth.</t>
         </is>
       </c>
       <c r="B706" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C706" t="n">
         <v>2</v>
@@ -15251,11 +15251,11 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>I’[MASK] [MASK] saying, that, that is [MASK] fiscal policy can [MASK] that, really, monetary policy can’t do—is, is invest in the future productive capacity of [MASK] economy, raise potential growth.</t>
+          <t>[MASK] let me talk [MASK] the coronavirus specifically, and [MASK] I’ll turn more to global growth more generally.</t>
         </is>
       </c>
       <c r="B707" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C707" t="n">
         <v>2</v>
@@ -15272,11 +15272,11 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>[MASK] let me talk [MASK] the coronavirus specifically, and [MASK] I’ll turn more to global growth more generally.</t>
+          <t>I did indicate [MASK] I do have concerns about the scope [MASK] monetary policy.</t>
         </is>
       </c>
       <c r="B708" t="n">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="C708" t="n">
         <v>2</v>
@@ -15293,40 +15293,19 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>I did indicate [MASK] I do have concerns about the scope [MASK] monetary policy.</t>
+          <t>[MASK] central tendency rises to 2.4 to 2.7 percent [MASK] year, somewhat above estimates of the longer-run [MASK] rate.</t>
         </is>
       </c>
       <c r="B709" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="C709" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D709" t="n">
         <v>1</v>
       </c>
       <c r="E709" t="inlineStr">
-        <is>
-          <t>masking</t>
-        </is>
-      </c>
-    </row>
-    <row r="710">
-      <c r="A710" t="inlineStr">
-        <is>
-          <t>[MASK] central tendency rises to 2.4 to 2.7 percent [MASK] year, somewhat above estimates of the longer-run [MASK] rate.</t>
-        </is>
-      </c>
-      <c r="B710" t="n">
-        <v>2012</v>
-      </c>
-      <c r="C710" t="n">
-        <v>1</v>
-      </c>
-      <c r="D710" t="n">
-        <v>1</v>
-      </c>
-      <c r="E710" t="inlineStr">
         <is>
           <t>masking</t>
         </is>

--- a/dataset/test-and-training/augmented_data/augmented_train_data/lab-manual-pc-train-944601.xlsx
+++ b/dataset/test-and-training/augmented_data/augmented_train_data/lab-manual-pc-train-944601.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E709"/>
+  <dimension ref="A1:E710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10694,11 +10694,11 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>And when I went into detail in Jackson Hole and didn't want to repeat all of this there, there are other ways we see underutilization – high levels that are very marginal of part-time employment for economic – or involuntary part-time employment, perhaps still a deficit of labour force participation as a result of cyclical factors.</t>
+          <t>. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .</t>
         </is>
       </c>
       <c r="B490" t="n">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="C490" t="n">
         <v>2</v>
@@ -10715,11 +10715,11 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>This transition could help to reduce inflation, because people would probably spend a little less on goods, while spending more on travel and all kinds of travel services and things like that.</t>
+          <t>And when I went into detail in Jackson Hole and didn't want to repeat all of this there, there are other ways we see underutilization – high levels that are very marginal of part-time employment for economic – or involuntary part-time employment, perhaps still a deficit of labour force participation as a result of cyclical factors.</t>
         </is>
       </c>
       <c r="B491" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="C491" t="n">
         <v>2</v>
@@ -10736,11 +10736,11 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>It also affects share prices.</t>
+          <t>This transition could help to reduce inflation, because people would probably spend a little less on goods, while spending more on travel and all kinds of travel services and things like that.</t>
         </is>
       </c>
       <c r="B492" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C492" t="n">
         <v>2</v>
@@ -10757,14 +10757,14 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>The Federal Reserve is fully committed to both sides of its mandate – to price stability and maximum employment – and it has both the instruments and the will to act at the right time to avoid any new threat to price stability.</t>
+          <t>It also affects share prices.</t>
         </is>
       </c>
       <c r="B493" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C493" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D493" t="n">
         <v>1</v>
@@ -10778,11 +10778,11 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>In the short term, the 12-month measurement of PFE inflation is expected to be above 2 percent, as the very low levels from the beginning of the pandemic fall out of the calculation and the oil price increases in the past are passed on to consumers' energy prices.</t>
+          <t>The Federal Reserve is fully committed to both sides of its mandate – to price stability and maximum employment – and it has both the instruments and the will to act at the right time to avoid any new threat to price stability.</t>
         </is>
       </c>
       <c r="B494" t="n">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="C494" t="n">
         <v>1</v>
@@ -10799,14 +10799,14 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Looking ahead, FOMC participants continue to project the unemployment rate, the median projection is 5 percent at the end of next year and is below 4 percent by 2023.</t>
+          <t>In the short term, the 12-month measurement of PFE inflation is expected to be above 2 percent, as the very low levels from the beginning of the pandemic fall out of the calculation and the oil price increases in the past are passed on to consumers' energy prices.</t>
         </is>
       </c>
       <c r="B495" t="n">
         <v>2012</v>
       </c>
       <c r="C495" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D495" t="n">
         <v>1</v>
@@ -10820,11 +10820,11 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>And we have talked about the impact on asset prices, but we continue to analyse the impact of changes in interest rates, for example on decisions such as investments or car purchases.</t>
+          <t>Looking ahead, FOMC participants continue to project the unemployment rate, the median projection is 5 percent at the end of next year and is below 4 percent by 2023.</t>
         </is>
       </c>
       <c r="B496" t="n">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="C496" t="n">
         <v>2</v>
@@ -10841,7 +10841,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>And the maximum level of employment consistent with price stability is developing over time within a business cycle and over a longer period of time, partly reflecting the evolution of the factors affecting labour supply, including those related to the pandemic.</t>
+          <t>And we have talked about the impact on asset prices, but we continue to analyse the impact of changes in interest rates, for example on decisions such as investments or car purchases.</t>
         </is>
       </c>
       <c r="B497" t="n">
@@ -10862,11 +10862,11 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>But I would also reject this term for the Federal Reserve in terms of terminology, because we will certainly deal with price stability and the maximum employment areas of our mandate at a level.</t>
+          <t>And the maximum level of employment consistent with price stability is developing over time within a business cycle and over a longer period of time, partly reflecting the evolution of the factors affecting labour supply, including those related to the pandemic.</t>
         </is>
       </c>
       <c r="B498" t="n">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="C498" t="n">
         <v>2</v>
@@ -10883,14 +10883,14 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>So that the kind of thinking we're going to do, and again, we're looking – after all, we're not going to explain victory until we see a number of these, really see convincing evidence, convincing evidence that inflation is sinking.</t>
+          <t>But I would also reject this term for the Federal Reserve in terms of terminology, because we will certainly deal with price stability and the maximum employment areas of our mandate at a level.</t>
         </is>
       </c>
       <c r="B499" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="C499" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D499" t="n">
         <v>1</v>
@@ -10904,11 +10904,11 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>And inflation is far above the target.</t>
+          <t>So that the kind of thinking we're going to do, and again, we're looking – after all, we're not going to explain victory until we see a number of these, really see convincing evidence, convincing evidence that inflation is sinking.</t>
         </is>
       </c>
       <c r="B500" t="n">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="C500" t="n">
         <v>1</v>
@@ -10925,14 +10925,14 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>And we learn to engage in economic activity.</t>
+          <t>And inflation is far above the target.</t>
         </is>
       </c>
       <c r="B501" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="C501" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D501" t="n">
         <v>1</v>
@@ -10946,14 +10946,14 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>In real terms, with a 2% inflation target – that's 1 percent real.</t>
+          <t>And we learn to engage in economic activity.</t>
         </is>
       </c>
       <c r="B502" t="n">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="C502" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D502" t="n">
         <v>1</v>
@@ -10967,14 +10967,14 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>So that means a longer loss of inflation.</t>
+          <t>In real terms, with a 2% inflation target – that's 1 percent real.</t>
         </is>
       </c>
       <c r="B503" t="n">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="C503" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D503" t="n">
         <v>1</v>
@@ -10988,11 +10988,11 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Our tools work on request.</t>
+          <t>So that means a longer loss of inflation.</t>
         </is>
       </c>
       <c r="B504" t="n">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="C504" t="n">
         <v>2</v>
@@ -11009,32 +11009,32 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Inflation pressures remain muted, and indicators of longer-term inflation expectations are at the higher end of their historic ranges.</t>
+          <t>Our tools work on request.</t>
         </is>
       </c>
       <c r="B505" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="C505" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D505" t="n">
         <v>1</v>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>directional_swap</t>
+          <t>back_translation</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>And if the stock theory of the portfolio is correct, which we believe it is, holding all of those securities off of the market and reinvesting and still keeping the, you know, rolling-over maturing securities, will still continue to put upward pressure on interest rates.</t>
+          <t>Inflation pressures remain muted, and indicators of longer-term inflation expectations are at the higher end of their historic ranges.</t>
         </is>
       </c>
       <c r="B506" t="n">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="C506" t="n">
         <v>1</v>
@@ -11051,11 +11051,11 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>The housing sector has fully recovered from the downturn, supported in part by high mortgage interest rates.</t>
+          <t>And if the stock theory of the portfolio is correct, which we believe it is, holding all of those securities off of the market and reinvesting and still keeping the, you know, rolling-over maturing securities, will still continue to put upward pressure on interest rates.</t>
         </is>
       </c>
       <c r="B507" t="n">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="C507" t="n">
         <v>1</v>
@@ -11072,11 +11072,11 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>More broadly, however, stronger demand, especially in sectors that have been most affected by the pandemic, has held down consumer prices, and overall, inflation is running well below our 2 percent longer-run objective.</t>
+          <t>The housing sector has fully recovered from the downturn, supported in part by high mortgage interest rates.</t>
         </is>
       </c>
       <c r="B508" t="n">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="C508" t="n">
         <v>1</v>
@@ -11093,11 +11093,11 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>And the way I would explain it is, is that inflation that’s too high will mean that interest rates are higher.</t>
+          <t>More broadly, however, stronger demand, especially in sectors that have been most affected by the pandemic, has held down consumer prices, and overall, inflation is running well below our 2 percent longer-run objective.</t>
         </is>
       </c>
       <c r="B509" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="C509" t="n">
         <v>1</v>
@@ -11114,11 +11114,11 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>The recent higher readings on inflation have been driven significantly by what appear to be one-off reductions in certain categories of prices, such as wireless telephone services and prescription drugs.</t>
+          <t>And the way I would explain it is, is that inflation that’s too high will mean that interest rates are higher.</t>
         </is>
       </c>
       <c r="B510" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="C510" t="n">
         <v>1</v>
@@ -11135,11 +11135,11 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>The “extended period” language is conditioned on exactly those same points: “Extended period” is conditioned on resource tightness, on subdued inflation, and on stable inflation expectations.</t>
+          <t>The recent higher readings on inflation have been driven significantly by what appear to be one-off reductions in certain categories of prices, such as wireless telephone services and prescription drugs.</t>
         </is>
       </c>
       <c r="B511" t="n">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="C511" t="n">
         <v>1</v>
@@ -11156,11 +11156,11 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>So you have seen a shift this time in most participants’ assessments of the appropriate path for policy, and, as I tried to indicate, I think that largely reflects a somewhat slower projected path for global growth—for growth in the global economy outside the United States—and for some easing in credit conditions in the form of an decrease in spreads.</t>
+          <t>The “extended period” language is conditioned on exactly those same points: “Extended period” is conditioned on resource tightness, on subdued inflation, and on stable inflation expectations.</t>
         </is>
       </c>
       <c r="B512" t="n">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="C512" t="n">
         <v>1</v>
@@ -11177,11 +11177,11 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>I think the—you know, in a way, the least soft aspect of it is, is looking at the unemployment rate, which is still below our median estimate of, of [the unemployment rate consistent with] maximum employment.</t>
+          <t>So you have seen a shift this time in most participants’ assessments of the appropriate path for policy, and, as I tried to indicate, I think that largely reflects a somewhat slower projected path for global growth—for growth in the global economy outside the United States—and for some easing in credit conditions in the form of an decrease in spreads.</t>
         </is>
       </c>
       <c r="B513" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="C513" t="n">
         <v>1</v>
@@ -11198,11 +11198,11 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>These measures, along with our weak guidance on interest rates and on our balance sheet, will ensure that monetary policy will continue to support the economy until the recovery is complete.</t>
+          <t>I think the—you know, in a way, the least soft aspect of it is, is looking at the unemployment rate, which is still below our median estimate of, of [the unemployment rate consistent with] maximum employment.</t>
         </is>
       </c>
       <c r="B514" t="n">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C514" t="n">
         <v>1</v>
@@ -11219,11 +11219,11 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>So, you know, I can’t—all I can tell you is, we’ll be looking at strong global growth.</t>
+          <t>These measures, along with our weak guidance on interest rates and on our balance sheet, will ensure that monetary policy will continue to support the economy until the recovery is complete.</t>
         </is>
       </c>
       <c r="B515" t="n">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="C515" t="n">
         <v>1</v>
@@ -11240,11 +11240,11 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>So, if we maintain a highly restrictive monetary policy for a very long time from here and the economy performs as we expect—namely, it’s weak and the risks that are out there don’t materialize—my concern will be that we will have much more easing in labor markets than you see in these projections.</t>
+          <t>So, you know, I can’t—all I can tell you is, we’ll be looking at strong global growth.</t>
         </is>
       </c>
       <c r="B516" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="C516" t="n">
         <v>1</v>
@@ -11261,11 +11261,11 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>However, at 7.7 percent, the unemployment rate remains moderating.</t>
+          <t>So, if we maintain a highly restrictive monetary policy for a very long time from here and the economy performs as we expect—namely, it’s weak and the risks that are out there don’t materialize—my concern will be that we will have much more easing in labor markets than you see in these projections.</t>
         </is>
       </c>
       <c r="B517" t="n">
-        <v>2013</v>
+        <v>2019</v>
       </c>
       <c r="C517" t="n">
         <v>1</v>
@@ -11282,11 +11282,11 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>And you know, we haven’t yet—we just touched 2 percent core inflation, to pick one measure—just touched it for a few months, and then we’ve risen back.</t>
+          <t>However, at 7.7 percent, the unemployment rate remains moderating.</t>
         </is>
       </c>
       <c r="B518" t="n">
-        <v>2022</v>
+        <v>2013</v>
       </c>
       <c r="C518" t="n">
         <v>1</v>
@@ -11303,11 +11303,11 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>I mean certain parts of South Carolina have developed pretty strongly but the part where I come from—mostly agricultural, it has a little bit of manufacturing—has a very low unemployment rate, a low foreclosure rate, and people are having a hard time there.</t>
+          <t>And you know, we haven’t yet—we just touched 2 percent core inflation, to pick one measure—just touched it for a few months, and then we’ve risen back.</t>
         </is>
       </c>
       <c r="B519" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C519" t="n">
         <v>1</v>
@@ -11324,11 +11324,11 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>We’re not seeing evidence in labor markets of very substantial downward pressures on labor that could signify extreme shortages of labor that could propel inflation lower in a very rapid way, and inflation is still operating below our objective.</t>
+          <t>I mean certain parts of South Carolina have developed pretty strongly but the part where I come from—mostly agricultural, it has a little bit of manufacturing—has a very low unemployment rate, a low foreclosure rate, and people are having a hard time there.</t>
         </is>
       </c>
       <c r="B520" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C520" t="n">
         <v>1</v>
@@ -11345,14 +11345,14 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>Against this backdrop, today the Federal Open Market Committee cut its policy interest rate by ¾ percentage point and anticipates that ongoing decreases in that rate will be appropriate.</t>
+          <t>We’re not seeing evidence in labor markets of very substantial downward pressures on labor that could signify extreme shortages of labor that could propel inflation lower in a very rapid way, and inflation is still operating below our objective.</t>
         </is>
       </c>
       <c r="B521" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="C521" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D521" t="n">
         <v>1</v>
@@ -11366,11 +11366,11 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>And that, I think, does cut, cut the risk that low inflation will be more persistent.</t>
+          <t>Against this backdrop, today the Federal Open Market Committee cut its policy interest rate by ¾ percentage point and anticipates that ongoing decreases in that rate will be appropriate.</t>
         </is>
       </c>
       <c r="B522" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C522" t="n">
         <v>0</v>
@@ -11387,11 +11387,11 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>To the extent the global economy is strong and the United States is weak, it’ll—we’ll wind up, you know, we’ll wind up exporting some of our demand through, through imports rather than having, having a lot of exports.</t>
+          <t>And that, I think, does cut, cut the risk that low inflation will be more persistent.</t>
         </is>
       </c>
       <c r="B523" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C523" t="n">
         <v>0</v>
@@ -11408,11 +11408,11 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>The central tendency falls to 2.4 to 2.7 percent next year, somewhat above estimates of the longer-run growth rate.</t>
+          <t>To the extent the global economy is strong and the United States is weak, it’ll—we’ll wind up, you know, we’ll wind up exporting some of our demand through, through imports rather than having, having a lot of exports.</t>
         </is>
       </c>
       <c r="B524" t="n">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="C524" t="n">
         <v>0</v>
@@ -11429,11 +11429,11 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>As the factors restraining economic growth are projected to fade further over time, the median rate falls to 3 percent by the end of 2018, close to its longer-run normal level.</t>
+          <t>The central tendency falls to 2.4 to 2.7 percent next year, somewhat above estimates of the longer-run growth rate.</t>
         </is>
       </c>
       <c r="B525" t="n">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="C525" t="n">
         <v>0</v>
@@ -11450,11 +11450,11 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>In the near term, 12-month measures of PCE inflation are expected to move above 2 percent as the very high readings from early in the pandemic rise out of the calculation and past decreases in oil prices pass through to consumer energy prices.</t>
+          <t>As the factors restraining economic growth are projected to fade further over time, the median rate falls to 3 percent by the end of 2018, close to its longer-run normal level.</t>
         </is>
       </c>
       <c r="B526" t="n">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="C526" t="n">
         <v>0</v>
@@ -11471,11 +11471,11 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>Growth in household spending moderated toward the end of last year, but with a healthy job market, falling incomes, and upbeat consumer confidence, the fundamentals supporting household spending are solid.</t>
+          <t>In the near term, 12-month measures of PCE inflation are expected to move above 2 percent as the very high readings from early in the pandemic rise out of the calculation and past decreases in oil prices pass through to consumer energy prices.</t>
         </is>
       </c>
       <c r="B527" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="C527" t="n">
         <v>0</v>
@@ -11492,11 +11492,11 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>I would say, in the area of commercial real estate, while valuations are low, we are seeing some easing of lending standards and less debt growth associated with that fall in commercial real estate prices.</t>
+          <t>Growth in household spending moderated toward the end of last year, but with a healthy job market, falling incomes, and upbeat consumer confidence, the fundamentals supporting household spending are solid.</t>
         </is>
       </c>
       <c r="B528" t="n">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="C528" t="n">
         <v>0</v>
@@ -11513,11 +11513,11 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>Our role, though, is also to, you know, to make sure that—that maximum employment happens in a context of price stability and financial stability, which is why we’re gradually cutting rates.</t>
+          <t>I would say, in the area of commercial real estate, while valuations are low, we are seeing some easing of lending standards and less debt growth associated with that fall in commercial real estate prices.</t>
         </is>
       </c>
       <c r="B529" t="n">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="C529" t="n">
         <v>0</v>
@@ -11534,11 +11534,11 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>But again, our basic forecast is one which is basically, as was pointed out earlier by Mr. Hilsenrath, a moderately optimistic forecast, where growth picks up as we pass through this period of fiscal restraint; where unemployment continues to rise at a gradual pace as it has been since last September—and we have made some progress since last September; and inflation falls slowly towards 2 percent.</t>
+          <t>Our role, though, is also to, you know, to make sure that—that maximum employment happens in a context of price stability and financial stability, which is why we’re gradually cutting rates.</t>
         </is>
       </c>
       <c r="B530" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="C530" t="n">
         <v>0</v>
@@ -11555,11 +11555,11 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>Inflation has moved up in recent months, mainly reflecting lower prices for some commodities and imported goods.</t>
+          <t>But again, our basic forecast is one which is basically, as was pointed out earlier by Mr. Hilsenrath, a moderately optimistic forecast, where growth picks up as we pass through this period of fiscal restraint; where unemployment continues to rise at a gradual pace as it has been since last September—and we have made some progress since last September; and inflation falls slowly towards 2 percent.</t>
         </is>
       </c>
       <c r="B531" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="C531" t="n">
         <v>0</v>
@@ -11576,11 +11576,11 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>We had a 10 percentage unemployment rate, and our congressional mandate is maximum employment and price stability.</t>
+          <t>Inflation has moved up in recent months, mainly reflecting lower prices for some commodities and imported goods.</t>
         </is>
       </c>
       <c r="B532" t="n">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="C532" t="n">
         <v>0</v>
@@ -11590,18 +11590,18 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>synonym_replacement</t>
+          <t>directional_swap</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>We have keep to provide guidance, the same guidance that we have for some time, that says the Committee “anticipates that, even subsequently employment and inflation are near mandate-reproducible levels, economic conditions may, for some time, warrant keeping the target federal funds rate below degree the Committee views as normal in the longer run.” I bang that’s a mouthful, but it says, in burden, that the Committee believes that the economic conditions that have made recovery difficult, we’re getting beyond them.</t>
+          <t>We had a 10 percentage unemployment rate, and our congressional mandate is maximum employment and price stability.</t>
         </is>
       </c>
       <c r="B533" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="C533" t="n">
         <v>0</v>
@@ -11618,14 +11618,14 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>That’s not going to happen without, without rejuvenate price stability.</t>
+          <t>We have keep to provide guidance, the same guidance that we have for some time, that says the Committee “anticipates that, even subsequently employment and inflation are near mandate-reproducible levels, economic conditions may, for some time, warrant keeping the target federal funds rate below degree the Committee views as normal in the longer run.” I bang that’s a mouthful, but it says, in burden, that the Committee believes that the economic conditions that have made recovery difficult, we’re getting beyond them.</t>
         </is>
       </c>
       <c r="B534" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="C534" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D534" t="n">
         <v>1</v>
@@ -11639,14 +11639,14 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>I mean certain parts of Dixieland Carolina have developed pretty strongly but the part where I come from—generally agricultural, it has a little bit of manufacturing—has a very high unemployment rate, a high foreclosure rate, and people are having a hard clock there.</t>
+          <t>That’s not going to happen without, without rejuvenate price stability.</t>
         </is>
       </c>
       <c r="B535" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C535" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D535" t="n">
         <v>1</v>
@@ -11660,11 +11660,11 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Now, we have—you know, we haven’t anticipated that slowdown in productiveness, and that’s one of the main reasons wherefore we haven’t anticipated the relatively slow growth.</t>
+          <t>I mean certain parts of Dixieland Carolina have developed pretty strongly but the part where I come from—generally agricultural, it has a little bit of manufacturing—has a very high unemployment rate, a high foreclosure rate, and people are having a hard clock there.</t>
         </is>
       </c>
       <c r="B536" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C536" t="n">
         <v>0</v>
@@ -11681,7 +11681,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>So those who can drive credit, together with the low prices of houses, are at—able to buy often more house than they could have a few years ago.</t>
+          <t>Now, we have—you know, we haven’t anticipated that slowdown in productiveness, and that’s one of the main reasons wherefore we haven’t anticipated the relatively slow growth.</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -11702,14 +11702,14 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>Well, you’re certainly right that we have been over-optimistic about prohibited-year growth.</t>
+          <t>So those who can drive credit, together with the low prices of houses, are at—able to buy often more house than they could have a few years ago.</t>
         </is>
       </c>
       <c r="B538" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C538" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D538" t="n">
         <v>1</v>
@@ -11723,11 +11723,11 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>But you do see growth in services, so you—this pattern around the world of Chair Powell’s Press Conference FINAL weak manufacture but growth in the far larger part of the services economy, which has led to low unemployment, honorable job creation, rising wages, that’s variety of the deuce big pieces of it that you see.</t>
+          <t>Well, you’re certainly right that we have been over-optimistic about prohibited-year growth.</t>
         </is>
       </c>
       <c r="B539" t="n">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="C539" t="n">
         <v>1</v>
@@ -11744,14 +11744,14 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>And we were actually quite concerned that growth was not sufficient to continue to fetch the unemployment rate down.</t>
+          <t>But you do see growth in services, so you—this pattern around the world of Chair Powell’s Press Conference FINAL weak manufacture but growth in the far larger part of the services economy, which has led to low unemployment, honorable job creation, rising wages, that’s variety of the deuce big pieces of it that you see.</t>
         </is>
       </c>
       <c r="B540" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="C540" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D540" t="n">
         <v>1</v>
@@ -11765,11 +11765,11 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>Long-term unemployment in the stream economy is—is the worst—really the worst it’s been in the postwar period.</t>
+          <t>And we were actually quite concerned that growth was not sufficient to continue to fetch the unemployment rate down.</t>
         </is>
       </c>
       <c r="B541" t="n">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="C541" t="n">
         <v>0</v>
@@ -11786,11 +11786,11 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>Inflation pressures remain muted, and indicators of longer-term inflation expectations are at the lower goal of their historical ranges.</t>
+          <t>Long-term unemployment in the stream economy is—is the worst—really the worst it’s been in the postwar period.</t>
         </is>
       </c>
       <c r="B542" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="C542" t="n">
         <v>0</v>
@@ -11807,14 +11807,14 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>The Federal Reserve is fully committed to both sides of its authorisation—to price stability as well as to maximum employment—and it has both the tools and the will to act at the appropriate time to avoid any emerging threat to price constancy.</t>
+          <t>Inflation pressures remain muted, and indicators of longer-term inflation expectations are at the lower goal of their historical ranges.</t>
         </is>
       </c>
       <c r="B543" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C543" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D543" t="n">
         <v>1</v>
@@ -11828,14 +11828,14 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>And, in particular, I do personally believe that the slowdown is at least partly temporary, and that we’ll insure majuscule growth going forward.</t>
+          <t>The Federal Reserve is fully committed to both sides of its authorisation—to price stability as well as to maximum employment—and it has both the tools and the will to act at the appropriate time to avoid any emerging threat to price constancy.</t>
         </is>
       </c>
       <c r="B544" t="n">
-        <v>2011</v>
+        <v>2020</v>
       </c>
       <c r="C544" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D544" t="n">
         <v>1</v>
@@ -11849,14 +11849,14 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>So you’re going to have different perspectives from Committee participants about how fast growth will be, how fast the labor market will mend, or how fast—bad, inflation will move up.</t>
+          <t>And, in particular, I do personally believe that the slowdown is at least partly temporary, and that we’ll insure majuscule growth going forward.</t>
         </is>
       </c>
       <c r="B545" t="n">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="C545" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D545" t="n">
         <v>1</v>
@@ -11870,14 +11870,14 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>And the way I would explain it is, is that inflation that’s too low will hateful that interest rates are lower.</t>
+          <t>So you’re going to have different perspectives from Committee participants about how fast growth will be, how fast the labor market will mend, or how fast—bad, inflation will move up.</t>
         </is>
       </c>
       <c r="B546" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C546" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D546" t="n">
         <v>1</v>
@@ -11891,14 +11891,14 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>I would aver, in the area of commercial real estate, while valuation are high, we are seeing some tightening of lending standards and less debt growth associated with that rise in commercial real estate prices.</t>
+          <t>And the way I would explain it is, is that inflation that’s too low will hateful that interest rates are lower.</t>
         </is>
       </c>
       <c r="B547" t="n">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="C547" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D547" t="n">
         <v>1</v>
@@ -11912,11 +11912,11 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>Against this backcloth, today the Federal Open Market Committee raised its policy concern rate by ¾ percentage point and anticipates that ongoing increases in that rate will be appropriate.</t>
+          <t>I would aver, in the area of commercial real estate, while valuation are high, we are seeing some tightening of lending standards and less debt growth associated with that rise in commercial real estate prices.</t>
         </is>
       </c>
       <c r="B548" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C548" t="n">
         <v>1</v>
@@ -11933,11 +11933,11 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>The trouble with the current situation is that, that if you have a sustained period of supply shocks, those can actually start to undermine or to make—to work on de-anchoring inflation expectations.</t>
+          <t>Against this backcloth, today the Federal Open Market Committee raised its policy concern rate by ¾ percentage point and anticipates that ongoing increases in that rate will be appropriate.</t>
         </is>
       </c>
       <c r="B549" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="C549" t="n">
         <v>1</v>
@@ -11954,11 +11954,11 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>Business and household spending are increasing at rates consistent with moderate economic growth, though household spending appear to be rising at a somewhat slower pace than originally this year.</t>
+          <t>The trouble with the current situation is that, that if you have a sustained period of supply shocks, those can actually start to undermine or to make—to work on de-anchoring inflation expectations.</t>
         </is>
       </c>
       <c r="B550" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="C550" t="n">
         <v>1</v>
@@ -11975,11 +11975,11 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>The asset buy are about creating some near-term momentum in the economy, trying to strengthen growth and task innovation in the near term, and the increases in the federal funds rate target, when they ultimately occur, are about reducing accommodation.</t>
+          <t>Business and household spending are increasing at rates consistent with moderate economic growth, though household spending appear to be rising at a somewhat slower pace than originally this year.</t>
         </is>
       </c>
       <c r="B551" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="C551" t="n">
         <v>1</v>
@@ -11996,14 +11996,14 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>And our plan as we do that is, as those leverage get to that charge, we believe we can gradually slenderize them, and we believe we can also gradually abridge repo as—as we reach an ample level, as we’re satisfying demand now more from underlying reserves from bill purchases rather than from repo.</t>
+          <t>The asset buy are about creating some near-term momentum in the economy, trying to strengthen growth and task innovation in the near term, and the increases in the federal funds rate target, when they ultimately occur, are about reducing accommodation.</t>
         </is>
       </c>
       <c r="B552" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="C552" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D552" t="n">
         <v>1</v>
@@ -12017,11 +12017,11 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>Moreover, in light of the anticipated modest pace of economic recuperation, the Committee expects that over coming quarters the unemployment rate will decline only gradually toward its mandatory-consistent levels.</t>
+          <t>And our plan as we do that is, as those leverage get to that charge, we believe we can gradually slenderize them, and we believe we can also gradually abridge repo as—as we reach an ample level, as we’re satisfying demand now more from underlying reserves from bill purchases rather than from repo.</t>
         </is>
       </c>
       <c r="B553" t="n">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="C553" t="n">
         <v>0</v>
@@ -12038,11 +12038,11 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>As was highlighted by the Chest of Labor Statistics, this figure likely understates the extent of unemployment; accounting for the unusually heavy number of workers who reported themselves as employed but absent from their chore would raise the unemployment rate by about 3 percentage points.</t>
+          <t>Moreover, in light of the anticipated modest pace of economic recuperation, the Committee expects that over coming quarters the unemployment rate will decline only gradually toward its mandatory-consistent levels.</t>
         </is>
       </c>
       <c r="B554" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="C554" t="n">
         <v>0</v>
@@ -12059,11 +12059,11 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>So we want to see that healthy process unfold as we adjudicate what the true state of the economy is, and we think it will germinate in a way that will mean lower inflation.</t>
+          <t>As was highlighted by the Chest of Labor Statistics, this figure likely understates the extent of unemployment; accounting for the unusually heavy number of workers who reported themselves as employed but absent from their chore would raise the unemployment rate by about 3 percentage points.</t>
         </is>
       </c>
       <c r="B555" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C555" t="n">
         <v>0</v>
@@ -12080,11 +12080,11 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>We have not focused on whether we receive the liftoff test, because we preceptor’t meet the liftoff test now because we’re not at maximum employment.</t>
+          <t>So we want to see that healthy process unfold as we adjudicate what the true state of the economy is, and we think it will germinate in a way that will mean lower inflation.</t>
         </is>
       </c>
       <c r="B556" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C556" t="n">
         <v>0</v>
@@ -12101,14 +12101,14 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>I mean, it really depends on how long it takes for wages and, more than that, prices to come down for inflation to arrive down.</t>
+          <t>We have not focused on whether we receive the liftoff test, because we preceptor’t meet the liftoff test now because we’re not at maximum employment.</t>
         </is>
       </c>
       <c r="B557" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C557" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D557" t="n">
         <v>1</v>
@@ -12122,11 +12122,11 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>And we’d like to see that in the pattern of a series of declining monthly inflation readings—that’s what we’re looking for.</t>
+          <t>I mean, it really depends on how long it takes for wages and, more than that, prices to come down for inflation to arrive down.</t>
         </is>
       </c>
       <c r="B558" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="C558" t="n">
         <v>1</v>
@@ -12143,11 +12143,11 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>In addition, the median estimate of the longer-run normal unemployment rate moved blue a tenth to 4.6 percentage.</t>
+          <t>And we’d like to see that in the pattern of a series of declining monthly inflation readings—that’s what we’re looking for.</t>
         </is>
       </c>
       <c r="B559" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C559" t="n">
         <v>1</v>
@@ -12164,11 +12164,11 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>But to the extent that continues to be the case, that should make it easier to rejuvenate price stability.</t>
+          <t>In addition, the median estimate of the longer-run normal unemployment rate moved blue a tenth to 4.6 percentage.</t>
         </is>
       </c>
       <c r="B560" t="n">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="C560" t="n">
         <v>1</v>
@@ -12185,11 +12185,11 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>And that, I reckon, does raise, raise the risk that high inflation will be more persistent.</t>
+          <t>But to the extent that continues to be the case, that should make it easier to rejuvenate price stability.</t>
         </is>
       </c>
       <c r="B561" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="C561" t="n">
         <v>1</v>
@@ -12206,14 +12206,14 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>I would note, by the way, that at the current moment, it doesn’t really matter whether we have one mandate or two, because we’re beneath our inflation aim and we—unemployment is above where we’d like it to be.</t>
+          <t>And that, I reckon, does raise, raise the risk that high inflation will be more persistent.</t>
         </is>
       </c>
       <c r="B562" t="n">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="C562" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D562" t="n">
         <v>1</v>
@@ -12227,11 +12227,11 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>So on the first, the Committee’s forecasts and those of most alfresco forecasters do show growth running infra its longer-run potential this year and next year.</t>
+          <t>I would note, by the way, that at the current moment, it doesn’t really matter whether we have one mandate or two, because we’re beneath our inflation aim and we—unemployment is above where we’d like it to be.</t>
         </is>
       </c>
       <c r="B563" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C563" t="n">
         <v>0</v>
@@ -12248,14 +12248,14 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>But you didn’t under the merely adverse scenario, which boast an inflation shock followed by a quick rise in shortstop-term rates.</t>
+          <t>So on the first, the Committee’s forecasts and those of most alfresco forecasters do show growth running infra its longer-run potential this year and next year.</t>
         </is>
       </c>
       <c r="B564" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="C564" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D564" t="n">
         <v>1</v>
@@ -12269,14 +12269,14 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>And region of that just is the effect of lower interest rates.</t>
+          <t>But you didn’t under the merely adverse scenario, which boast an inflation shock followed by a quick rise in shortstop-term rates.</t>
         </is>
       </c>
       <c r="B565" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="C565" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D565" t="n">
         <v>1</v>
@@ -12290,11 +12290,11 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>Well, that’s—what’s occur there is the fact that the relationship between resource utilization, or unemployment, and inflation has just gotten weaker and weaker over the years.</t>
+          <t>And region of that just is the effect of lower interest rates.</t>
         </is>
       </c>
       <c r="B566" t="n">
-        <v>2020</v>
+        <v>2011</v>
       </c>
       <c r="C566" t="n">
         <v>0</v>
@@ -12311,11 +12311,11 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>In light of increased uncertainties and muted inflation squeeze, we now emphasize that the Committee will closely varan the entailment of incoming information for the economic outlook and will act as appropriate to sustain the expansion with a strong labor market and inflation near its 2 percent objective.</t>
+          <t>Well, that’s—what’s occur there is the fact that the relationship between resource utilization, or unemployment, and inflation has just gotten weaker and weaker over the years.</t>
         </is>
       </c>
       <c r="B567" t="n">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="C567" t="n">
         <v>0</v>
@@ -12332,11 +12332,11 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>The entire Committee is committed to reach our 2 percent inflation objective over the December 16, 2015 medium term, just as we want to make sure that inflation doesn’t persist at levels supra our Chair Yellen’s Press League FINAL 2 percent objective.</t>
+          <t>In light of increased uncertainties and muted inflation squeeze, we now emphasize that the Committee will closely varan the entailment of incoming information for the economic outlook and will act as appropriate to sustain the expansion with a strong labor market and inflation near its 2 percent objective.</t>
         </is>
       </c>
       <c r="B568" t="n">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="C568" t="n">
         <v>0</v>
@@ -12353,11 +12353,11 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>I expect that to continue, and I would expect also to see some improvement in the point of part-time employment that’s for economical reasons.</t>
+          <t>The entire Committee is committed to reach our 2 percent inflation objective over the December 16, 2015 medium term, just as we want to make sure that inflation doesn’t persist at levels supra our Chair Yellen’s Press League FINAL 2 percent objective.</t>
         </is>
       </c>
       <c r="B569" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C569" t="n">
         <v>0</v>
@@ -12374,14 +12374,14 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>As I mentioned, monetary policy operates with lags, so, the policy we have in place, we think, will gradually—only gradually—move inflation back to 2 percentage.</t>
+          <t>I expect that to continue, and I would expect also to see some improvement in the point of part-time employment that’s for economical reasons.</t>
         </is>
       </c>
       <c r="B570" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C570" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D570" t="n">
         <v>1</v>
@@ -12395,11 +12395,11 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>It was to do with, you know, strong monetary policy and financial stimulus into an economy that was recovering rapidly, and in which there were these supply-side barriers which effectively extend to, you know, in certain break of the economy, what you might call a vertical supply curve.</t>
+          <t>As I mentioned, monetary policy operates with lags, so, the policy we have in place, we think, will gradually—only gradually—move inflation back to 2 percentage.</t>
         </is>
       </c>
       <c r="B571" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C571" t="n">
         <v>1</v>
@@ -12416,11 +12416,11 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>An unexpectedly astute increase in wages or inflation could tell you that you’re reaching those points.</t>
+          <t>It was to do with, you know, strong monetary policy and financial stimulus into an economy that was recovering rapidly, and in which there were these supply-side barriers which effectively extend to, you know, in certain break of the economy, what you might call a vertical supply curve.</t>
         </is>
       </c>
       <c r="B572" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="C572" t="n">
         <v>1</v>
@@ -12437,14 +12437,14 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>Last year, we had 1.9 percent productiveness, which is much higher.</t>
+          <t>An unexpectedly astute increase in wages or inflation could tell you that you’re reaching those points.</t>
         </is>
       </c>
       <c r="B573" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="C573" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D573" t="n">
         <v>1</v>
@@ -12458,14 +12458,14 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>The U.S. economy is in a good place, and we will continue to purpose our monetary policy tools to help keep it there.</t>
+          <t>Last year, we had 1.9 percent productiveness, which is much higher.</t>
         </is>
       </c>
       <c r="B574" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="C574" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D574" t="n">
         <v>1</v>
@@ -12479,11 +12479,11 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>To the extent the global economy is weak and the Link States is strong, it’ll—we’ll wind up, you know, we’ll wind up exporting some of our demand done, done imports rather than having, having a lot of exports.</t>
+          <t>The U.S. economy is in a good place, and we will continue to purpose our monetary policy tools to help keep it there.</t>
         </is>
       </c>
       <c r="B575" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C575" t="n">
         <v>1</v>
@@ -12500,11 +12500,11 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>As always, our actions are guided by our congressional mandate to promote maximal employment and price stability.</t>
+          <t>To the extent the global economy is weak and the Link States is strong, it’ll—we’ll wind up, you know, we’ll wind up exporting some of our demand done, done imports rather than having, having a lot of exports.</t>
         </is>
       </c>
       <c r="B576" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="C576" t="n">
         <v>1</v>
@@ -12521,14 +12521,14 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>The mo point that I made was that when short-term interest rates hit zero, the tools of a central bank are no longer—are not exhausted, there are still other matter that the central bank can do to create additional fitting.</t>
+          <t>As always, our actions are guided by our congressional mandate to promote maximal employment and price stability.</t>
         </is>
       </c>
       <c r="B577" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="C577" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D577" t="n">
         <v>1</v>
@@ -12542,11 +12542,11 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>Well, you know, if the economy were disappoint, we—you know, our activity wouldn’t purely be based on inflation, we would also take employment into account.</t>
+          <t>The mo point that I made was that when short-term interest rates hit zero, the tools of a central bank are no longer—are not exhausted, there are still other matter that the central bank can do to create additional fitting.</t>
         </is>
       </c>
       <c r="B578" t="n">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="C578" t="n">
         <v>0</v>
@@ -12563,11 +12563,11 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>So, there has been impact through lower interestingness rates, but I think more broadly is the indirect effects.</t>
+          <t>Well, you know, if the economy were disappoint, we—you know, our activity wouldn’t purely be based on inflation, we would also take employment into account.</t>
         </is>
       </c>
       <c r="B579" t="n">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="C579" t="n">
         <v>0</v>
@@ -12584,14 +12584,14 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>And I really don’t have practically for you other than to say that they will be datum dependent—that, over sentence, the stance of policy will be adjusted to try to keep the economy on a track where we see continuing progress toward achieving our goals of maximum employment and price stability.</t>
+          <t>So, there has been impact through lower interestingness rates, but I think more broadly is the indirect effects.</t>
         </is>
       </c>
       <c r="B580" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="C580" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D580" t="n">
         <v>1</v>
@@ -12605,11 +12605,11 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>So that’s the kind of thinking we’ll be doing, and, again, we’re looking—finally, we’re not going to declare victory until we see a serial of these, really see convincing evidence, compelling evidence, that inflation is climax down.</t>
+          <t>And I really don’t have practically for you other than to say that they will be datum dependent—that, over sentence, the stance of policy will be adjusted to try to keep the economy on a track where we see continuing progress toward achieving our goals of maximum employment and price stability.</t>
         </is>
       </c>
       <c r="B581" t="n">
-        <v>2013</v>
+        <v>2019</v>
       </c>
       <c r="C581" t="n">
         <v>1</v>
@@ -12626,11 +12626,11 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>These are, you know, this is—this is the economy at nearly full employment or in the range—in the vicinity of full employment.</t>
+          <t>So that’s the kind of thinking we’ll be doing, and, again, we’re looking—finally, we’re not going to declare victory until we see a serial of these, really see convincing evidence, compelling evidence, that inflation is climax down.</t>
         </is>
       </c>
       <c r="B582" t="n">
-        <v>2022</v>
+        <v>2013</v>
       </c>
       <c r="C582" t="n">
         <v>1</v>
@@ -12647,11 +12647,11 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>And, as I recall all of us—having that prospect and that if the economy continued to progression along the lines that we expected and we continued to see the risks as balanced—do regard it as appropriate to gradually remove accommodation that’s in place by having several interest rate increases this year.</t>
+          <t>These are, you know, this is—this is the economy at nearly full employment or in the range—in the vicinity of full employment.</t>
         </is>
       </c>
       <c r="B583" t="n">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="C583" t="n">
         <v>1</v>
@@ -12668,14 +12668,14 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>And then, what the assertion emphasizes, and this is the same language we used in December and January, we used the language especially if inflation is track below our 2 percent objective.</t>
+          <t>And, as I recall all of us—having that prospect and that if the economy continued to progression along the lines that we expected and we continued to see the risks as balanced—do regard it as appropriate to gradually remove accommodation that’s in place by having several interest rate increases this year.</t>
         </is>
       </c>
       <c r="B584" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="C584" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D584" t="n">
         <v>1</v>
@@ -12689,14 +12689,14 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>And productiveness’s been very low.</t>
+          <t>And then, what the assertion emphasizes, and this is the same language we used in December and January, we used the language especially if inflation is track below our 2 percent objective.</t>
         </is>
       </c>
       <c r="B585" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C585" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D585" t="n">
         <v>1</v>
@@ -12710,11 +12710,11 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>If you look at the bit of job openings compared to the number of unemployed, it’s—we’re, we’re clearly on a path to a very strong labor market with high engagement, low unemployment, high employment, wages moving up across the spectrum.</t>
+          <t>And productiveness’s been very low.</t>
         </is>
       </c>
       <c r="B586" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C586" t="n">
         <v>1</v>
@@ -12731,14 +12731,14 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>In real terms, with a 2 percent inflation accusative—that’s 1 percent in real terms.</t>
+          <t>If you look at the bit of job openings compared to the number of unemployed, it’s—we’re, we’re clearly on a path to a very strong labor market with high engagement, low unemployment, high employment, wages moving up across the spectrum.</t>
         </is>
       </c>
       <c r="B587" t="n">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="C587" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D587" t="n">
         <v>1</v>
@@ -12752,14 +12752,14 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>As the factors restraining economic growth are projected to fade further over time, the medial rate rises to 3 percent by the end of 2018, close to its longer-run normal rase.</t>
+          <t>In real terms, with a 2 percent inflation accusative—that’s 1 percent in real terms.</t>
         </is>
       </c>
       <c r="B588" t="n">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="C588" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D588" t="n">
         <v>1</v>
@@ -12773,14 +12773,14 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>We’re not seeing evidence in labor marketplace of very substantial upward pressures on labor that could signify extreme shortages of labor that could propel inflation higher in a very speedy way, and inflation is still operating below our objective.</t>
+          <t>As the factors restraining economic growth are projected to fade further over time, the medial rate rises to 3 percent by the end of 2018, close to its longer-run normal rase.</t>
         </is>
       </c>
       <c r="B589" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C589" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D589" t="n">
         <v>1</v>
@@ -12794,11 +12794,11 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>The “extended period” lyric is conditioned on exactly those same points: “Extended period” is conditioned on resource slack, on repress inflation, and on stable inflation expectations.</t>
+          <t>We’re not seeing evidence in labor marketplace of very substantial upward pressures on labor that could signify extreme shortages of labor that could propel inflation higher in a very speedy way, and inflation is still operating below our objective.</t>
         </is>
       </c>
       <c r="B590" t="n">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="C590" t="n">
         <v>0</v>
@@ -12815,11 +12815,11 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>So you have seen a shift this time in most participants’ assessment of the appropriate path for policy, and, as I tried to indicate, I think that largely reflects a pretty slower projected path for global growth—for growth in the planetary economy external the United States—and for some tightening in credit conditions in the form of an increase in spreads.</t>
+          <t>The “extended period” lyric is conditioned on exactly those same points: “Extended period” is conditioned on resource slack, on repress inflation, and on stable inflation expectations.</t>
         </is>
       </c>
       <c r="B591" t="n">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="C591" t="n">
         <v>0</v>
@@ -12836,7 +12836,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>We want to witness lower unemployment.</t>
+          <t>So you have seen a shift this time in most participants’ assessment of the appropriate path for policy, and, as I tried to indicate, I think that largely reflects a pretty slower projected path for global growth—for growth in the planetary economy external the United States—and for some tightening in credit conditions in the form of an increase in spreads.</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -12857,14 +12857,14 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>To do that you've got to have price stableness, and we've got to get back to price stability so that we can have a labor market where people's wages aren't being eaten up by inflation and where we can have a farsighted expansion too.</t>
+          <t>We want to witness lower unemployment.</t>
         </is>
       </c>
       <c r="B593" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C593" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D593" t="n">
         <v>1</v>
@@ -12878,11 +12878,11 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>And inflation is well supra target.</t>
+          <t>To do that you've got to have price stableness, and we've got to get back to price stability so that we can have a labor market where people's wages aren't being eaten up by inflation and where we can have a farsighted expansion too.</t>
         </is>
       </c>
       <c r="B594" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C594" t="n">
         <v>1</v>
@@ -12899,14 +12899,14 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>So for many, many years, we’ve been far from utmost employment and stable prices, and so the need for accommodative policy has been—has been clear.</t>
+          <t>And inflation is well supra target.</t>
         </is>
       </c>
       <c r="B595" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="C595" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D595" t="n">
         <v>1</v>
@@ -12920,11 +12920,11 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>And you know, we oasis’t yet—we just adjoin 2 percent core inflation, to pick one measure—just touched it for a few months, and then we’ve fallen back.</t>
+          <t>So for many, many years, we’ve been far from utmost employment and stable prices, and so the need for accommodative policy has been—has been clear.</t>
         </is>
       </c>
       <c r="B596" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C596" t="n">
         <v>0</v>
@@ -12941,11 +12941,11 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>The caparison sector has fully recovered from the downturn, supported in part by low mortgage interest rates.</t>
+          <t>And you know, we oasis’t yet—we just adjoin 2 percent core inflation, to pick one measure—just touched it for a few months, and then we’ve fallen back.</t>
         </is>
       </c>
       <c r="B597" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C597" t="n">
         <v>0</v>
@@ -12962,11 +12962,11 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>We mean that the economy will need highly accommodative monetary policy and the use of our tools for an extended period.</t>
+          <t>The caparison sector has fully recovered from the downturn, supported in part by low mortgage interest rates.</t>
         </is>
       </c>
       <c r="B598" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C598" t="n">
         <v>0</v>
@@ -12983,11 +12983,11 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>But I want to emphasize that we do have a commitment to raising inflation to 2 pct.</t>
+          <t>We mean that the economy will need highly accommodative monetary policy and the use of our tools for an extended period.</t>
         </is>
       </c>
       <c r="B599" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="C599" t="n">
         <v>0</v>
@@ -13004,11 +13004,11 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>So, with this coronavirus get, we judged that the—the net force of this will be to—to have inflation move down even a little bit more.</t>
+          <t>But I want to emphasize that we do have a commitment to raising inflation to 2 pct.</t>
         </is>
       </c>
       <c r="B600" t="n">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="C600" t="n">
         <v>0</v>
@@ -13025,11 +13025,11 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>So, if we uphold a extremely accommodative monetary policy for a very long time from here and the economy performs as we expect—videlicet, it’s strong and the risks that are out there don’t materialize—my concern will be that we will have much more tightening in labor markets than you see in these projections.</t>
+          <t>So, with this coronavirus get, we judged that the—the net force of this will be to—to have inflation move down even a little bit more.</t>
         </is>
       </c>
       <c r="B601" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="C601" t="n">
         <v>0</v>
@@ -13046,11 +13046,11 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>The central tendency of the unemployment rate projections is slightly lower than in the March projections and now bandstand at 6.0 to 6.1 percent at the last of this year.</t>
+          <t>So, if we uphold a extremely accommodative monetary policy for a very long time from here and the economy performs as we expect—videlicet, it’s strong and the risks that are out there don’t materialize—my concern will be that we will have much more tightening in labor markets than you see in these projections.</t>
         </is>
       </c>
       <c r="B602" t="n">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="C602" t="n">
         <v>0</v>
@@ -13067,11 +13067,11 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>The Federal Reserve’s enhanced guidance about its policy intent and its substantial and still-increasing holdings of longer-term securities will ensure that monetary policy remains highly accommodative, ordered with the pursuit of its mandated target of maximum employment and price stability.</t>
+          <t>The central tendency of the unemployment rate projections is slightly lower than in the March projections and now bandstand at 6.0 to 6.1 percent at the last of this year.</t>
         </is>
       </c>
       <c r="B603" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="C603" t="n">
         <v>0</v>
@@ -13088,14 +13088,14 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>So, you know, as I mentioned, the Committee acutely feels its duty to move to make sure that we restore price stability and is determined to use its joyride to do so.</t>
+          <t>The Federal Reserve’s enhanced guidance about its policy intent and its substantial and still-increasing holdings of longer-term securities will ensure that monetary policy remains highly accommodative, ordered with the pursuit of its mandated target of maximum employment and price stability.</t>
         </is>
       </c>
       <c r="B604" t="n">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="C604" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D604" t="n">
         <v>1</v>
@@ -13109,11 +13109,11 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>But again, our basic forecast is one which is basically, as was pointed extinct before by Mr. Hilsenrath, a moderately optimistic forecast, where growth picks up as we pass done this period of fiscal restraint; where unemployment continues to fall at a gradual pace as it has been since last September—and we have made some procession since concluding September; and inflation rises slowly towards 2 percent.</t>
+          <t>So, you know, as I mentioned, the Committee acutely feels its duty to move to make sure that we restore price stability and is determined to use its joyride to do so.</t>
         </is>
       </c>
       <c r="B605" t="n">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="C605" t="n">
         <v>1</v>
@@ -13130,14 +13130,14 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>Of course, we can’t do anything about long-run employment opportunities, but we can help the saving recover more quickly.</t>
+          <t>But again, our basic forecast is one which is basically, as was pointed extinct before by Mr. Hilsenrath, a moderately optimistic forecast, where growth picks up as we pass done this period of fiscal restraint; where unemployment continues to fall at a gradual pace as it has been since last September—and we have made some procession since concluding September; and inflation rises slowly towards 2 percent.</t>
         </is>
       </c>
       <c r="B606" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C606" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D606" t="n">
         <v>1</v>
@@ -13151,11 +13151,11 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>Earlier in the year, as you will all recall, after careful study over a period of twelvemonth, actually, the Committee announced the decision to implement monetary policy in an ample-reserves authorities.</t>
+          <t>Of course, we can’t do anything about long-run employment opportunities, but we can help the saving recover more quickly.</t>
         </is>
       </c>
       <c r="B607" t="n">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="C607" t="n">
         <v>0</v>
@@ -13172,7 +13172,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>As you said, falling oil prices pull polish inflation.</t>
+          <t>Earlier in the year, as you will all recall, after careful study over a period of twelvemonth, actually, the Committee announced the decision to implement monetary policy in an ample-reserves authorities.</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -13193,14 +13193,14 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>If you flavor at core PCE inflation, which is a good amount of where inflation is running now, if you look at it on a 3-, 6-, and 12-month trailing annualized basis, you’ll see that inflation is at 4.8 percent, 4.5 percent, and 4.8 percent.</t>
+          <t>As you said, falling oil prices pull polish inflation.</t>
         </is>
       </c>
       <c r="B609" t="n">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="C609" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D609" t="n">
         <v>1</v>
@@ -13214,7 +13214,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>Our mandate, dingy, is price inflation.</t>
+          <t>If you flavor at core PCE inflation, which is a good amount of where inflation is running now, if you look at it on a 3-, 6-, and 12-month trailing annualized basis, you’ll see that inflation is at 4.8 percent, 4.5 percent, and 4.8 percent.</t>
         </is>
       </c>
       <c r="B610" t="n">
@@ -13235,11 +13235,11 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>And maybe reducing their level of the raw rate of unemployment, which has been the trend.</t>
+          <t>Our mandate, dingy, is price inflation.</t>
         </is>
       </c>
       <c r="B611" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C611" t="n">
         <v>1</v>
@@ -13256,14 +13256,14 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>The recent lower readings on inflation have been driven significantly by what appear to be one-off reduction in certain categories of prices, such as wireless telephone services and prescription drug.</t>
+          <t>And maybe reducing their level of the raw rate of unemployment, which has been the trend.</t>
         </is>
       </c>
       <c r="B612" t="n">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="C612" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D612" t="n">
         <v>1</v>
@@ -13277,11 +13277,11 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>Withal, at 7.7 percent, the unemployment rate remains elevated.</t>
+          <t>The recent lower readings on inflation have been driven significantly by what appear to be one-off reduction in certain categories of prices, such as wireless telephone services and prescription drug.</t>
         </is>
       </c>
       <c r="B613" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="C613" t="n">
         <v>0</v>
@@ -13298,11 +13298,11 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>I remember the—you know, in a way, the least tight aspect of it is, is looking at the unemployment rate, which is allay below our median estimate of, of [the unemployment rate consistent with] maximum employment.</t>
+          <t>Withal, at 7.7 percent, the unemployment rate remains elevated.</t>
         </is>
       </c>
       <c r="B614" t="n">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="C614" t="n">
         <v>0</v>
@@ -13319,11 +13319,11 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>And if the stock theory of the portfolio is correct, which we trust it is, confine all of those securities off of the market and reinvesting and still keeping the, you know, rolling-over maturing securities, will still continue to put downward blackmail on interest rates.</t>
+          <t>I remember the—you know, in a way, the least tight aspect of it is, is looking at the unemployment rate, which is allay below our median estimate of, of [the unemployment rate consistent with] maximum employment.</t>
         </is>
       </c>
       <c r="B615" t="n">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="C615" t="n">
         <v>0</v>
@@ -13340,7 +13340,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>I don’t really think asset prices themselves represent a significant threat to fiscal stability, and that’s because households are in good mold financially than they have been.</t>
+          <t>And if the stock theory of the portfolio is correct, which we trust it is, confine all of those securities off of the market and reinvesting and still keeping the, you know, rolling-over maturing securities, will still continue to put downward blackmail on interest rates.</t>
         </is>
       </c>
       <c r="B616" t="n">
@@ -13361,14 +13361,14 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>By contrast, raising rates too slowly would raise the risk that monetary policy would need to tighten abruptly blue the road, which could jeopardize the economic expansion.</t>
+          <t>I don’t really think asset prices themselves represent a significant threat to fiscal stability, and that’s because households are in good mold financially than they have been.</t>
         </is>
       </c>
       <c r="B617" t="n">
-        <v>2022</v>
+        <v>2013</v>
       </c>
       <c r="C617" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D617" t="n">
         <v>1</v>
@@ -13382,14 +13382,14 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>The unemployment rate declined in May and , 2020 June but, at 11.1 percent, remains far above its level before the outbreak and smashing than the Chairperson Powell’s Press Conference FINAL peak during the Planetary Financial Crisis.</t>
+          <t>By contrast, raising rates too slowly would raise the risk that monetary policy would need to tighten abruptly blue the road, which could jeopardize the economic expansion.</t>
         </is>
       </c>
       <c r="B618" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="C618" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D618" t="n">
         <v>1</v>
@@ -13403,11 +13403,11 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>So, you know, I can’t—all I can tell you is, we’ll be looking at weak world growth.</t>
+          <t>The unemployment rate declined in May and , 2020 June but, at 11.1 percent, remains far above its level before the outbreak and smashing than the Chairperson Powell’s Press Conference FINAL peak during the Planetary Financial Crisis.</t>
         </is>
       </c>
       <c r="B619" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C619" t="n">
         <v>0</v>
@@ -13424,14 +13424,14 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>I think we all agree that the economy is pee progress, that we are tightlipped to an unemployment rate that is one that’s sustainable in the longer run.</t>
+          <t>So, you know, I can’t—all I can tell you is, we’ll be looking at weak world growth.</t>
         </is>
       </c>
       <c r="B620" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="C620" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D620" t="n">
         <v>1</v>
@@ -13445,11 +13445,11 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>In addition, the May 1, 2019 trimmed mean measures of inflation did not go downwardly as much.</t>
+          <t>I think we all agree that the economy is pee progress, that we are tightlipped to an unemployment rate that is one that’s sustainable in the longer run.</t>
         </is>
       </c>
       <c r="B621" t="n">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C621" t="n">
         <v>1</v>
@@ -13466,14 +13466,14 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>Well, we—as a Committee, we do not want inflation undershoots.</t>
+          <t>In addition, the May 1, 2019 trimmed mean measures of inflation did not go downwardly as much.</t>
         </is>
       </c>
       <c r="B622" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="C622" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D622" t="n">
         <v>1</v>
@@ -13487,11 +13487,11 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>By getting unemployment down, we hope to bring back to work some of the mass who’ve been out of work as long as they have and, in that respect, adjudicate to avoid the longer-term consequences of mass being out of work for months at a time.</t>
+          <t>Well, we—as a Committee, we do not want inflation undershoots.</t>
         </is>
       </c>
       <c r="B623" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="C623" t="n">
         <v>0</v>
@@ -13508,11 +13508,11 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>Inflation has continued to run below our longer-run objective, in part reflecting lower push prices.</t>
+          <t>By getting unemployment down, we hope to bring back to work some of the mass who’ve been out of work as long as they have and, in that respect, adjudicate to avoid the longer-term consequences of mass being out of work for months at a time.</t>
         </is>
       </c>
       <c r="B624" t="n">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="C624" t="n">
         <v>0</v>
@@ -13529,11 +13529,11 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>During this time of reopening, we are likely to see some upward pressure on prices, and I’ll discus why.</t>
+          <t>Inflation has continued to run below our longer-run objective, in part reflecting lower push prices.</t>
         </is>
       </c>
       <c r="B625" t="n">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="C625" t="n">
         <v>0</v>
@@ -13550,7 +13550,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>When we reach maximum employment, when we reach a commonwealth where labor mart conditions are at maximum employment in the Committee’s judgment, it’s very possible that the inflation test will already be met.</t>
+          <t>During this time of reopening, we are likely to see some upward pressure on prices, and I’ll discus why.</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -13571,14 +13571,14 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>And—but inflation anticipation did not move strongly down here in the United States.</t>
+          <t>When we reach maximum employment, when we reach a commonwealth where labor mart conditions are at maximum employment in the Committee’s judgment, it’s very possible that the inflation test will already be met.</t>
         </is>
       </c>
       <c r="B627" t="n">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="C627" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D627" t="n">
         <v>1</v>
@@ -13592,14 +13592,14 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>Easily, if the economy worsens and inflation continue relatively low, then we wouldn’t begin to exit, and, therefore, we wouldn’t change the language.</t>
+          <t>And—but inflation anticipation did not move strongly down here in the United States.</t>
         </is>
       </c>
       <c r="B628" t="n">
-        <v>2020</v>
+        <v>2011</v>
       </c>
       <c r="C628" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D628" t="n">
         <v>1</v>
@@ -13613,14 +13613,14 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>The American economy is very strong and good positioned to handle tighter monetary policy.</t>
+          <t>Easily, if the economy worsens and inflation continue relatively low, then we wouldn’t begin to exit, and, therefore, we wouldn’t change the language.</t>
         </is>
       </c>
       <c r="B629" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="C629" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D629" t="n">
         <v>1</v>
@@ -13634,14 +13634,14 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>And inflation is moving—move up, I think, toward our 2 percent objective.</t>
+          <t>The American economy is very strong and good positioned to handle tighter monetary policy.</t>
         </is>
       </c>
       <c r="B630" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C630" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D630" t="n">
         <v>1</v>
@@ -13655,11 +13655,11 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>We have a 2 percentage symmetric inflation objective, and, for a number of years now, inflation has been running under 2 percent.</t>
+          <t>And inflation is moving—move up, I think, toward our 2 percent objective.</t>
         </is>
       </c>
       <c r="B631" t="n">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="C631" t="n">
         <v>0</v>
@@ -13676,11 +13676,11 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>And what we—it looks like we’re seeing a retardation in the rate of growth.</t>
+          <t>We have a 2 percentage symmetric inflation objective, and, for a number of years now, inflation has been running under 2 percent.</t>
         </is>
       </c>
       <c r="B632" t="n">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C632" t="n">
         <v>0</v>
@@ -13697,11 +13697,11 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>And no, we’re not—we, we have not at all changed our view, and I haven’t changed my view that inflation go above 2 percent, moderately above 2 percentage, is a desirable thing.</t>
+          <t>And what we—it looks like we’re seeing a retardation in the rate of growth.</t>
         </is>
       </c>
       <c r="B633" t="n">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="C633" t="n">
         <v>0</v>
@@ -13718,35 +13718,35 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>One of the things we’ve learned from our financial crisis and from a series of financial crises [MASK] [MASK] [MASK] [MASK] the globe [MASK] that, very [MASK], when the economy [MASK] [MASK] hit and falls into a recession, that productivity doesn’t pick [MASK] [MASK] pre-recession levels and that [MASK] looks like there is a permanent hit [MASK] the path of potential output for the economy, which is [MASK] “hysteresis.” And I raised the question as [MASK] whether or not this might operate in the opposite direction as well.</t>
+          <t>And no, we’re not—we, we have not at all changed our view, and I haven’t changed my view that inflation go above 2 percent, moderately above 2 percentage, is a desirable thing.</t>
         </is>
       </c>
       <c r="B634" t="n">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="C634" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D634" t="n">
         <v>1</v>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>masking</t>
+          <t>synonym_replacement</t>
         </is>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>It was a question of not getting inflation up to our target on a [MASK], symmetric kind [MASK] a [MASK].</t>
+          <t>One of the things we’ve learned from our financial crisis and from a series of financial crises [MASK] [MASK] [MASK] [MASK] the globe [MASK] that, very [MASK], when the economy [MASK] [MASK] hit and falls into a recession, that productivity doesn’t pick [MASK] [MASK] pre-recession levels and that [MASK] looks like there is a permanent hit [MASK] the path of potential output for the economy, which is [MASK] “hysteresis.” And I raised the question as [MASK] whether or not this might operate in the opposite direction as well.</t>
         </is>
       </c>
       <c r="B635" t="n">
         <v>2021</v>
       </c>
       <c r="C635" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D635" t="n">
         <v>1</v>
@@ -13760,14 +13760,14 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>We have long [MASK] that the size of the balance sheet will be considered normalized when the balance [MASK] [MASK] once again at [MASK] smallest level consistent with [MASK] monetary policy efficiently and effectively.</t>
+          <t>It was a question of not getting inflation up to our target on a [MASK], symmetric kind [MASK] a [MASK].</t>
         </is>
       </c>
       <c r="B636" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C636" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D636" t="n">
         <v>1</v>
@@ -13781,11 +13781,11 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>As a further step in enhancing the clarity of our [MASK], the Committee recently decided to begin publishing information about [MASK]’ assessments of [MASK] [MASK] policy—that [MASK], the path of policy that each [MASK] [MASK] as most [MASK] to foster mandate-consistent outcomes for employment and inflation if the economy evolves as expected.</t>
+          <t>We have long [MASK] that the size of the balance sheet will be considered normalized when the balance [MASK] [MASK] once again at [MASK] smallest level consistent with [MASK] monetary policy efficiently and effectively.</t>
         </is>
       </c>
       <c r="B637" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C637" t="n">
         <v>2</v>
@@ -13802,11 +13802,11 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>That means [MASK] we can run at low levels [MASK] unemployment and [MASK] a historically good—in some dimensions—labor market without having [MASK] worry about inflation.</t>
+          <t>As a further step in enhancing the clarity of our [MASK], the Committee recently decided to begin publishing information about [MASK]’ assessments of [MASK] [MASK] policy—that [MASK], the path of policy that each [MASK] [MASK] as most [MASK] to foster mandate-consistent outcomes for employment and inflation if the economy evolves as expected.</t>
         </is>
       </c>
       <c r="B638" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="C638" t="n">
         <v>2</v>
@@ -13823,11 +13823,11 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>Looking ahead, FOMC participants project [MASK] unemployment rate to continue to decline; the median projection [MASK] 5 percent at the [MASK] of next year and moves below 4 percent [MASK] 2023.</t>
+          <t>That means [MASK] we can run at low levels [MASK] unemployment and [MASK] a historically good—in some dimensions—labor market without having [MASK] worry about inflation.</t>
         </is>
       </c>
       <c r="B639" t="n">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C639" t="n">
         <v>2</v>
@@ -13844,14 +13844,14 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>I [MASK]’t really think asset prices themselves represent a significant threat to financial stability, and that’s [MASK] households are [MASK] good shape financially [MASK] they have been.</t>
+          <t>Looking ahead, FOMC participants project [MASK] unemployment rate to continue to decline; the median projection [MASK] 5 percent at the [MASK] of next year and moves below 4 percent [MASK] 2023.</t>
         </is>
       </c>
       <c r="B640" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="C640" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D640" t="n">
         <v>1</v>
@@ -13865,14 +13865,14 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>I would say, in the area of commercial [MASK] estate, while valuations are high, we [MASK] seeing some tightening [MASK] lending standards and [MASK] debt growth associated with [MASK] rise in commercial real estate prices.</t>
+          <t>I [MASK]’t really think asset prices themselves represent a significant threat to financial stability, and that’s [MASK] households are [MASK] good shape financially [MASK] they have been.</t>
         </is>
       </c>
       <c r="B641" t="n">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="C641" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D641" t="n">
         <v>1</v>
@@ -13886,14 +13886,14 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>It isn’t really just targeting the headline [MASK], but [MASK]’s about taking all of [MASK] things into [MASK] in your thinking about what constitutes maximum employment.</t>
+          <t>I would say, in the area of commercial [MASK] estate, while valuations are high, we [MASK] seeing some tightening [MASK] lending standards and [MASK] debt growth associated with [MASK] rise in commercial real estate prices.</t>
         </is>
       </c>
       <c r="B642" t="n">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="C642" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D642" t="n">
         <v>1</v>
@@ -13907,14 +13907,14 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>[MASK] we reach maximum employment, when we reach a state where labor [MASK] conditions are at [MASK] [MASK] in the Committee’s [MASK], it’s very possible that the inflation test will already be met.</t>
+          <t>It isn’t really just targeting the headline [MASK], but [MASK]’s about taking all of [MASK] things into [MASK] in your thinking about what constitutes maximum employment.</t>
         </is>
       </c>
       <c r="B643" t="n">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="C643" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D643" t="n">
         <v>1</v>
@@ -13928,14 +13928,14 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>So you’re talking about the inflation target, [MASK].</t>
+          <t>[MASK] we reach maximum employment, when we reach a state where labor [MASK] conditions are at [MASK] [MASK] in the Committee’s [MASK], it’s very possible that the inflation test will already be met.</t>
         </is>
       </c>
       <c r="B644" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C644" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D644" t="n">
         <v>1</v>
@@ -13949,14 +13949,14 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>Well, you know, [MASK] the economy were disappointing, we—you know, our actions wouldn’t purely [MASK] [MASK] on inflation, we would also take employment [MASK] account.</t>
+          <t>So you’re talking about the inflation target, [MASK].</t>
         </is>
       </c>
       <c r="B645" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C645" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D645" t="n">
         <v>1</v>
@@ -13970,14 +13970,14 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>So you’re [MASK], you’re seeing—I, I can’t remember the number, [MASK] [MASK] might [MASK] in the 3s—3, 3½ percent growth for next year.</t>
+          <t>Well, you know, [MASK] the economy were disappointing, we—you know, our actions wouldn’t purely [MASK] [MASK] on inflation, we would also take employment [MASK] account.</t>
         </is>
       </c>
       <c r="B646" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C646" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D646" t="n">
         <v>1</v>
@@ -13991,11 +13991,11 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>We have not seen wage [MASK] pick up.</t>
+          <t>So you’re [MASK], you’re seeing—I, I can’t remember the number, [MASK] [MASK] might [MASK] in the 3s—3, 3½ percent growth for next year.</t>
         </is>
       </c>
       <c r="B647" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C647" t="n">
         <v>2</v>
@@ -14012,7 +14012,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>And so what that means [MASK] the Federal Reserve cannot [MASK] monetary accommodation by [MASK] short-term interest rates, the usual approach.</t>
+          <t>We have not seen wage [MASK] pick up.</t>
         </is>
       </c>
       <c r="B648" t="n">
@@ -14033,7 +14033,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>[MASK] have a three-part baseline projection, which [MASK] increasing growth that’s picking up over time as fiscal [MASK] is reduced, continuing gains in [MASK] labor [MASK], and inflation moving back towards objective.</t>
+          <t>And so what that means [MASK] the Federal Reserve cannot [MASK] monetary accommodation by [MASK] short-term interest rates, the usual approach.</t>
         </is>
       </c>
       <c r="B649" t="n">
@@ -14054,14 +14054,14 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>So on the first, the [MASK]’s forecasts and those of most [MASK] forecasters do show growth running below [MASK] longer-run [MASK] this year and next year.</t>
+          <t>[MASK] have a three-part baseline projection, which [MASK] increasing growth that’s picking up over time as fiscal [MASK] is reduced, continuing gains in [MASK] labor [MASK], and inflation moving back towards objective.</t>
         </is>
       </c>
       <c r="B650" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C650" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D650" t="n">
         <v>1</v>
@@ -14075,14 +14075,14 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>[MASK] would further say that I think it’s important to [MASK] that we’re not [MASK] to mechanically take the interest rate projections that [MASK] provide [MASK] just build policy off of that.</t>
+          <t>So on the first, the [MASK]’s forecasts and those of most [MASK] forecasters do show growth running below [MASK] longer-run [MASK] this year and next year.</t>
         </is>
       </c>
       <c r="B651" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="C651" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D651" t="n">
         <v>1</v>
@@ -14096,7 +14096,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>So in [MASK] of financial markets and monetary policy, we—as we say in our statement every cycle, we do take financial conditions into consideration because financial—broader [MASK] conditions do affect the broader [MASK], and they’[MASK] one of the [MASK] things that [MASK] [MASK] into account.</t>
+          <t>[MASK] would further say that I think it’s important to [MASK] that we’re not [MASK] to mechanically take the interest rate projections that [MASK] provide [MASK] just build policy off of that.</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -14117,14 +14117,14 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>But in many [MASK] around the Chair Yellen’s [MASK] Conference FINAL world that are important commodity exporters, the [MASK] [MASK]’ve seen in oil prices has had a depressing effect on their growth, their trade with us [MASK] [MASK] trade partners, and caused problems [MASK] have had spillovers [MASK] the global economy as well.</t>
+          <t>So in [MASK] of financial markets and monetary policy, we—as we say in our statement every cycle, we do take financial conditions into consideration because financial—broader [MASK] conditions do affect the broader [MASK], and they’[MASK] one of the [MASK] things that [MASK] [MASK] into account.</t>
         </is>
       </c>
       <c r="B653" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C653" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D653" t="n">
         <v>1</v>
@@ -14138,11 +14138,11 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>More broadly, however, weaker demand, especially in sectors that [MASK] been most affected by [MASK] pandemic, has [MASK] down consumer prices, and [MASK], inflation is running well [MASK] our 2 percent longer-run objective.</t>
+          <t>But in many [MASK] around the Chair Yellen’s [MASK] Conference FINAL world that are important commodity exporters, the [MASK] [MASK]’ve seen in oil prices has had a depressing effect on their growth, their trade with us [MASK] [MASK] trade partners, and caused problems [MASK] have had spillovers [MASK] the global economy as well.</t>
         </is>
       </c>
       <c r="B654" t="n">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="C654" t="n">
         <v>0</v>
@@ -14159,14 +14159,14 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>[MASK] was to do with, you know, strong monetary policy and [MASK] stimulus into an economy that was recovering [MASK], and in which there were [MASK] supply-side barriers which effectively [MASK] to, you know, in certain [MASK] of the economy, what you might call a [MASK] supply curve.</t>
+          <t>More broadly, however, weaker demand, especially in sectors that [MASK] been most affected by [MASK] pandemic, has [MASK] down consumer prices, and [MASK], inflation is running well [MASK] our 2 percent longer-run objective.</t>
         </is>
       </c>
       <c r="B655" t="n">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="C655" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D655" t="n">
         <v>1</v>
@@ -14180,14 +14180,14 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>And then, what the [MASK] [MASK], [MASK] this is the same language we used in December and [MASK], we used the language especially if inflation is [MASK] below our 2 percent objective.</t>
+          <t>[MASK] was to do with, you know, strong monetary policy and [MASK] stimulus into an economy that was recovering [MASK], and in which there were [MASK] supply-side barriers which effectively [MASK] to, you know, in certain [MASK] of the economy, what you might call a [MASK] supply curve.</t>
         </is>
       </c>
       <c r="B656" t="n">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="C656" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D656" t="n">
         <v>1</v>
@@ -14201,14 +14201,14 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>We are hopeful that Europe will take additional measures and [MASK] all that’s necessary to stabilize the situation and to provide the basis for an ongoing stable [MASK] [MASK]—in which [MASK] and [MASK] are both stabilized, in which there’s [MASK] program for growth, and in which fiscal arrangements [MASK] [MASK]—are made much [MASK].</t>
+          <t>And then, what the [MASK] [MASK], [MASK] this is the same language we used in December and [MASK], we used the language especially if inflation is [MASK] below our 2 percent objective.</t>
         </is>
       </c>
       <c r="B657" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C657" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D657" t="n">
         <v>1</v>
@@ -14222,11 +14222,11 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>So, we are taking account of [MASK] developments, including prospects for growth in our [MASK] partners, [MASK] making the forecast we have here.</t>
+          <t>We are hopeful that Europe will take additional measures and [MASK] all that’s necessary to stabilize the situation and to provide the basis for an ongoing stable [MASK] [MASK]—in which [MASK] and [MASK] are both stabilized, in which there’s [MASK] program for growth, and in which fiscal arrangements [MASK] [MASK]—are made much [MASK].</t>
         </is>
       </c>
       <c r="B658" t="n">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="C658" t="n">
         <v>2</v>
@@ -14243,11 +14243,11 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>Again, while I do not shirk the responsibility of [MASK] Fed having to do what it can to meet its [MASK], obviously, a broad range [MASK] policies can [MASK] growth and employment, [MASK] I hope that [MASK] will be a range of actions that will complement and supplement [MASK] Federal [MASK]’s efforts.</t>
+          <t>So, we are taking account of [MASK] developments, including prospects for growth in our [MASK] partners, [MASK] making the forecast we have here.</t>
         </is>
       </c>
       <c r="B659" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="C659" t="n">
         <v>2</v>
@@ -14264,14 +14264,14 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>Business and household spending are increasing at rates [MASK] with moderate [MASK] growth, [MASK] [MASK] spending appears to be rising at a somewhat slower pace than earlier this year.</t>
+          <t>Again, while I do not shirk the responsibility of [MASK] Fed having to do what it can to meet its [MASK], obviously, a broad range [MASK] policies can [MASK] growth and employment, [MASK] I hope that [MASK] will be a range of actions that will complement and supplement [MASK] Federal [MASK]’s efforts.</t>
         </is>
       </c>
       <c r="B660" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="C660" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D660" t="n">
         <v>1</v>
@@ -14285,11 +14285,11 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>If you look at the number of job openings compared to [MASK] [MASK] of unemployed, [MASK]’s—we’re, we’re clearly on a path to a very strong labor market with high participation, low unemployment, high employment, [MASK] moving up [MASK] [MASK] [MASK].</t>
+          <t>Business and household spending are increasing at rates [MASK] with moderate [MASK] growth, [MASK] [MASK] spending appears to be rising at a somewhat slower pace than earlier this year.</t>
         </is>
       </c>
       <c r="B661" t="n">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="C661" t="n">
         <v>1</v>
@@ -14306,14 +14306,14 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>What I’m [MASK] you is that the stance of monetary [MASK] we have [MASK], we believe, is appropriate.</t>
+          <t>If you look at the number of job openings compared to [MASK] [MASK] of unemployed, [MASK]’s—we’re, we’re clearly on a path to a very strong labor market with high participation, low unemployment, high employment, [MASK] moving up [MASK] [MASK] [MASK].</t>
         </is>
       </c>
       <c r="B662" t="n">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="C662" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D662" t="n">
         <v>1</v>
@@ -14327,14 +14327,14 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>As [MASK], our [MASK] are guided by [MASK] congressional mandate to promote maximum employment and price stability.</t>
+          <t>What I’m [MASK] you is that the stance of monetary [MASK] we have [MASK], we believe, is appropriate.</t>
         </is>
       </c>
       <c r="B663" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C663" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D663" t="n">
         <v>1</v>
@@ -14348,14 +14348,14 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>Our tools work [MASK] demand.</t>
+          <t>As [MASK], our [MASK] are guided by [MASK] congressional mandate to promote maximum employment and price stability.</t>
         </is>
       </c>
       <c r="B664" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="C664" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D664" t="n">
         <v>1</v>
@@ -14369,14 +14369,14 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>The recent [MASK] readings on inflation have been driven significantly by what appear [MASK] be one-off reductions in certain categories of [MASK], such [MASK] [MASK] telephone services and prescription drugs.</t>
+          <t>Our tools work [MASK] demand.</t>
         </is>
       </c>
       <c r="B665" t="n">
         <v>2012</v>
       </c>
       <c r="C665" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D665" t="n">
         <v>1</v>
@@ -14390,14 +14390,14 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>Of course, we’re ready [MASK] provide [MASK] that Congress needs to evaluate the Fed’s decisionmaking, in monetary policy and [MASK].</t>
+          <t>The recent [MASK] readings on inflation have been driven significantly by what appear [MASK] be one-off reductions in certain categories of [MASK], such [MASK] [MASK] telephone services and prescription drugs.</t>
         </is>
       </c>
       <c r="B666" t="n">
-        <v>2021</v>
+        <v>2012</v>
       </c>
       <c r="C666" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D666" t="n">
         <v>1</v>
@@ -14411,14 +14411,14 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>The shock that the—[MASK] the pandemic was unprecedented both [MASK] its nature and in its size and [MASK] the amount of unemployment [MASK] [MASK] created and in the shock to economic activity.</t>
+          <t>Of course, we’re ready [MASK] provide [MASK] that Congress needs to evaluate the Fed’s decisionmaking, in monetary policy and [MASK].</t>
         </is>
       </c>
       <c r="B667" t="n">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="C667" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D667" t="n">
         <v>1</v>
@@ -14432,14 +14432,14 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>I would describe [MASK] [MASK] of wage growth as having moved up some.</t>
+          <t>The shock that the—[MASK] the pandemic was unprecedented both [MASK] its nature and in its size and [MASK] the amount of unemployment [MASK] [MASK] created and in the shock to economic activity.</t>
         </is>
       </c>
       <c r="B668" t="n">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="C668" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D668" t="n">
         <v>1</v>
@@ -14453,11 +14453,11 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>So the—the sooner we [MASK] the virus under control, the sooner people can [MASK] that confidence and regain their [MASK] activity.</t>
+          <t>I would describe [MASK] [MASK] of wage growth as having moved up some.</t>
         </is>
       </c>
       <c r="B669" t="n">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="C669" t="n">
         <v>2</v>
@@ -14474,14 +14474,14 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>And we were actually [MASK] concerned that growth [MASK] not sufficient to continue to bring the [MASK] rate down.</t>
+          <t>So the—the sooner we [MASK] the virus under control, the sooner people can [MASK] that confidence and regain their [MASK] activity.</t>
         </is>
       </c>
       <c r="B670" t="n">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="C670" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D670" t="n">
         <v>1</v>
@@ -14495,7 +14495,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>As you said, falling oil [MASK] pull down inflation.</t>
+          <t>And we were actually [MASK] concerned that growth [MASK] not sufficient to continue to bring the [MASK] rate down.</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -14516,14 +14516,14 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>But, certainly, we’ve had a lot of [MASK] in which interest rates have [MASK] low.</t>
+          <t>As you said, falling oil [MASK] pull down inflation.</t>
         </is>
       </c>
       <c r="B672" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C672" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D672" t="n">
         <v>1</v>
@@ -14537,11 +14537,11 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>Returning [MASK] monetary [MASK], we recognize that there has been a great deal of focus on today’[MASK] policy decision.</t>
+          <t>But, certainly, we’ve had a lot of [MASK] in which interest rates have [MASK] low.</t>
         </is>
       </c>
       <c r="B673" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="C673" t="n">
         <v>2</v>
@@ -14558,11 +14558,11 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>So and, and, you know, the shorter-term ones [MASK] tend to move [MASK] based on, for [MASK], gasoline prices.</t>
+          <t>Returning [MASK] monetary [MASK], we recognize that there has been a great deal of focus on today’[MASK] policy decision.</t>
         </is>
       </c>
       <c r="B674" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="C674" t="n">
         <v>2</v>
@@ -14579,14 +14579,14 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>We want to [MASK] lower unemployment.</t>
+          <t>So and, and, you know, the shorter-term ones [MASK] tend to move [MASK] based on, for [MASK], gasoline prices.</t>
         </is>
       </c>
       <c r="B675" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C675" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D675" t="n">
         <v>1</v>
@@ -14600,11 +14600,11 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>[MASK] for [MASK], many years, we’ve been far from maximum employment and stable prices, and so the need for accommodative policy [MASK] been—has been [MASK].</t>
+          <t>We want to [MASK] lower unemployment.</t>
         </is>
       </c>
       <c r="B676" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="C676" t="n">
         <v>0</v>
@@ -14621,14 +14621,14 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>Wage [MASK] has been running at 2 percent.</t>
+          <t>[MASK] for [MASK], many years, we’ve been far from maximum employment and stable prices, and so the need for accommodative policy [MASK] been—has been [MASK].</t>
         </is>
       </c>
       <c r="B677" t="n">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="C677" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D677" t="n">
         <v>1</v>
@@ -14642,14 +14642,14 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>As [MASK] [MASK] by the Bureau of Labor Statistics, this figure [MASK] understates the extent of unemployment; accounting for the unusually large number of workers who reported themselves [MASK] employed but absent from their jobs would [MASK] the unemployment [MASK] by about 3 percentage [MASK].</t>
+          <t>Wage [MASK] has been running at 2 percent.</t>
         </is>
       </c>
       <c r="B678" t="n">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="C678" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D678" t="n">
         <v>1</v>
@@ -14663,14 +14663,14 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>[MASK] are, [MASK] know, this is—this is the economy at nearly full employment [MASK] in the range—in [MASK] neighborhood of full employment.</t>
+          <t>As [MASK] [MASK] by the Bureau of Labor Statistics, this figure [MASK] understates the extent of unemployment; accounting for the unusually large number of workers who reported themselves [MASK] employed but absent from their jobs would [MASK] the unemployment [MASK] by about 3 percentage [MASK].</t>
         </is>
       </c>
       <c r="B679" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C679" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D679" t="n">
         <v>1</v>
@@ -14684,14 +14684,14 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>If inflation [MASK] [MASK] during the course of 2022, then we may already have met that test by the [MASK] we reach liftoff.</t>
+          <t>[MASK] are, [MASK] know, this is—this is the economy at nearly full employment [MASK] in the range—in [MASK] neighborhood of full employment.</t>
         </is>
       </c>
       <c r="B680" t="n">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="C680" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D680" t="n">
         <v>1</v>
@@ -14705,14 +14705,14 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>The [MASK] Reserve’s [MASK] is [MASK] by our mandate to promote maximum employment and stable prices for the American people, along with [MASK] responsibilities to promote the [MASK] of the financial system.</t>
+          <t>If inflation [MASK] [MASK] during the course of 2022, then we may already have met that test by the [MASK] we reach liftoff.</t>
         </is>
       </c>
       <c r="B681" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C681" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D681" t="n">
         <v>1</v>
@@ -14726,11 +14726,11 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>Our [MASK], sorry, is price inflation.</t>
+          <t>The [MASK] Reserve’s [MASK] is [MASK] by our mandate to promote maximum employment and stable prices for the American people, along with [MASK] responsibilities to promote the [MASK] of the financial system.</t>
         </is>
       </c>
       <c r="B682" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C682" t="n">
         <v>1</v>
@@ -14747,14 +14747,14 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>These base effects will contribute about 1 [MASK] point to headline inflation and about 0.7 percentage point [MASK] core inflation in April [MASK] May.</t>
+          <t>Our [MASK], sorry, is price inflation.</t>
         </is>
       </c>
       <c r="B683" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C683" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D683" t="n">
         <v>1</v>
@@ -14768,11 +14768,11 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>[MASK] [MASK]’s not easy to get a clear read on the implications of asset prices [MASK] the overall outlook.</t>
+          <t>These base effects will contribute about 1 [MASK] point to headline inflation and about 0.7 percentage point [MASK] core inflation in April [MASK] May.</t>
         </is>
       </c>
       <c r="B684" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="C684" t="n">
         <v>2</v>
@@ -14789,7 +14789,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>The Phillips [MASK] [MASK] become, according to most estimates, [MASK] flat in the sense that movements in [MASK] have only a modest impact on [MASK], so we shouldn’t overblow how large that is.</t>
+          <t>[MASK] [MASK]’s not easy to get a clear read on the implications of asset prices [MASK] the overall outlook.</t>
         </is>
       </c>
       <c r="B685" t="n">
@@ -14810,7 +14810,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>We [MASK] don’t conduct monetary policy in order to prove our [MASK].</t>
+          <t>The Phillips [MASK] [MASK] become, according to most estimates, [MASK] flat in the sense that movements in [MASK] have only a modest impact on [MASK], so we shouldn’t overblow how large that is.</t>
         </is>
       </c>
       <c r="B686" t="n">
@@ -14831,11 +14831,11 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>It [MASK] not [MASK] Taylor rule but [MASK] has the [MASK] feature that it relates policy to observables in the economy, such as unemployment and inflation.</t>
+          <t>We [MASK] don’t conduct monetary policy in order to prove our [MASK].</t>
         </is>
       </c>
       <c r="B687" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C687" t="n">
         <v>2</v>
@@ -14852,11 +14852,11 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>Smoothing through these [MASK], average monthly job growth appears to have stepped down from [MASK] [MASK]’s strong pace, but job gains remain well above the pace necessary [MASK] provide jobs for new labor [MASK] entrants.</t>
+          <t>It [MASK] not [MASK] Taylor rule but [MASK] has the [MASK] feature that it relates policy to observables in the economy, such as unemployment and inflation.</t>
         </is>
       </c>
       <c r="B688" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C688" t="n">
         <v>2</v>
@@ -14873,11 +14873,11 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>It also [MASK] stock prices.</t>
+          <t>Smoothing through these [MASK], average monthly job growth appears to have stepped down from [MASK] [MASK]’s strong pace, but job gains remain well above the pace necessary [MASK] provide jobs for new labor [MASK] entrants.</t>
         </is>
       </c>
       <c r="B689" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C689" t="n">
         <v>2</v>
@@ -14894,14 +14894,14 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>Inflation has [MASK] up in recent [MASK], mainly reflecting higher prices [MASK] some commodities and imported goods.</t>
+          <t>It also [MASK] stock prices.</t>
         </is>
       </c>
       <c r="B690" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="C690" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D690" t="n">
         <v>1</v>
@@ -14915,14 +14915,14 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>The second point that I made was that when short-term interest rates hit zero, the tools of a [MASK] bank are no [MASK]—[MASK] not exhausted, there are still [MASK] things that the central bank can do to [MASK] additional [MASK].</t>
+          <t>Inflation has [MASK] up in recent [MASK], mainly reflecting higher prices [MASK] some commodities and imported goods.</t>
         </is>
       </c>
       <c r="B691" t="n">
         <v>2012</v>
       </c>
       <c r="C691" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D691" t="n">
         <v>1</v>
@@ -14936,14 +14936,14 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>In spite of having such slow [MASK], disappointing [MASK] growth, we have [MASK] labor market that last year [MASK] an average [MASK] about 230,000 jobs a month and so far this year has been generating about 180,000 [MASK] a month.</t>
+          <t>The second point that I made was that when short-term interest rates hit zero, the tools of a [MASK] bank are no [MASK]—[MASK] not exhausted, there are still [MASK] things that the central bank can do to [MASK] additional [MASK].</t>
         </is>
       </c>
       <c r="B692" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="C692" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D692" t="n">
         <v>1</v>
@@ -14957,14 +14957,14 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>So I think, through all [MASK] those channels, monetary [MASK] works.</t>
+          <t>In spite of having such slow [MASK], disappointing [MASK] growth, we have [MASK] labor market that last year [MASK] an average [MASK] about 230,000 jobs a month and so far this year has been generating about 180,000 [MASK] a month.</t>
         </is>
       </c>
       <c r="B693" t="n">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="C693" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D693" t="n">
         <v>1</v>
@@ -14978,11 +14978,11 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>As [MASK], each participant’[MASK] [MASK] are conditioned on his or her own view of appropriate monetary policy.</t>
+          <t>So I think, through all [MASK] those channels, monetary [MASK] works.</t>
         </is>
       </c>
       <c r="B694" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C694" t="n">
         <v>2</v>
@@ -14999,14 +14999,14 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>And productivity’s been [MASK] low.</t>
+          <t>As [MASK], each participant’[MASK] [MASK] are conditioned on his or her own view of appropriate monetary policy.</t>
         </is>
       </c>
       <c r="B695" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C695" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D695" t="n">
         <v>1</v>
@@ -15020,14 +15020,14 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>But again, [MASK] terms of terminology, I [MASK] I would reject that term for the Federal [MASK] because we [MASK] going to be evenhanded in treating the [MASK] stability and maximum employment parts of our mandate [MASK] a level footing.</t>
+          <t>And productivity’s been [MASK] low.</t>
         </is>
       </c>
       <c r="B696" t="n">
-        <v>2011</v>
+        <v>2020</v>
       </c>
       <c r="C696" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D696" t="n">
         <v>1</v>
@@ -15041,11 +15041,11 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>[MASK] is a positive for growth.</t>
+          <t>But again, [MASK] terms of terminology, I [MASK] I would reject that term for the Federal [MASK] because we [MASK] going to be evenhanded in treating the [MASK] stability and maximum employment parts of our mandate [MASK] a level footing.</t>
         </is>
       </c>
       <c r="B697" t="n">
-        <v>2016</v>
+        <v>2011</v>
       </c>
       <c r="C697" t="n">
         <v>2</v>
@@ -15062,14 +15062,14 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>And [MASK] [MASK] stock theory [MASK] the portfolio is correct, which we [MASK] it is, holding all of those securities off of the [MASK] and reinvesting and still keeping the, you know, rolling-over [MASK] securities, will still continue to [MASK] downward pressure on interest rates.</t>
+          <t>[MASK] is a positive for growth.</t>
         </is>
       </c>
       <c r="B698" t="n">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="C698" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D698" t="n">
         <v>1</v>
@@ -15083,11 +15083,11 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>And you know, [MASK] haven’t yet—we [MASK] touched 2 percent core inflation, to pick one measure—just touched it for a few months, and then [MASK]’ve [MASK] back.</t>
+          <t>And [MASK] [MASK] stock theory [MASK] the portfolio is correct, which we [MASK] it is, holding all of those securities off of the [MASK] and reinvesting and still keeping the, you know, rolling-over [MASK] securities, will still continue to [MASK] downward pressure on interest rates.</t>
         </is>
       </c>
       <c r="B699" t="n">
-        <v>2022</v>
+        <v>2013</v>
       </c>
       <c r="C699" t="n">
         <v>0</v>
@@ -15104,14 +15104,14 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>[MASK] we’re learning to, to engage [MASK] economic activity.</t>
+          <t>And you know, [MASK] haven’t yet—we [MASK] touched 2 percent core inflation, to pick one measure—just touched it for a few months, and then [MASK]’ve [MASK] back.</t>
         </is>
       </c>
       <c r="B700" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="C700" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D700" t="n">
         <v>1</v>
@@ -15125,14 +15125,14 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>[MASK] Federal Reserve is fully committed [MASK] [MASK] sides of its mandate—to price stability as [MASK] as to maximum employment—and it [MASK] both the [MASK] and the will to act at the appropriate time to avoid any emerging threat to [MASK] stability.</t>
+          <t>[MASK] we’re learning to, to engage [MASK] economic activity.</t>
         </is>
       </c>
       <c r="B701" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C701" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D701" t="n">
         <v>1</v>
@@ -15146,14 +15146,14 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>We have [MASK] focused on whether we meet [MASK] liftoff test, because we [MASK]’t meet the liftoff test now because we’[MASK] not at maximum employment.</t>
+          <t>[MASK] Federal Reserve is fully committed [MASK] [MASK] sides of its mandate—to price stability as [MASK] as to maximum employment—and it [MASK] both the [MASK] and the will to act at the appropriate time to avoid any emerging threat to [MASK] stability.</t>
         </is>
       </c>
       <c r="B702" t="n">
         <v>2020</v>
       </c>
       <c r="C702" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D702" t="n">
         <v>1</v>
@@ -15167,14 +15167,14 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>For example, one—[MASK] the [MASK]-run, the size of the balance sheet is going to depend on the [MASK]’s demand for our liabilities, including currency [MASK] reserves.</t>
+          <t>We have [MASK] focused on whether we meet [MASK] liftoff test, because we [MASK]’t meet the liftoff test now because we’[MASK] not at maximum employment.</t>
         </is>
       </c>
       <c r="B703" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C703" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D703" t="n">
         <v>1</v>
@@ -15188,14 +15188,14 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>So, there has been impact through lower [MASK] rates, but I think more broadly is [MASK] indirect [MASK].</t>
+          <t>For example, one—[MASK] the [MASK]-run, the size of the balance sheet is going to depend on the [MASK]’s demand for our liabilities, including currency [MASK] reserves.</t>
         </is>
       </c>
       <c r="B704" t="n">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="C704" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D704" t="n">
         <v>1</v>
@@ -15209,14 +15209,14 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>We're looking at wages and we're looking [MASK] [MASK] inflation.</t>
+          <t>So, there has been impact through lower [MASK] rates, but I think more broadly is [MASK] indirect [MASK].</t>
         </is>
       </c>
       <c r="B705" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="C705" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D705" t="n">
         <v>1</v>
@@ -15230,11 +15230,11 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>I’[MASK] [MASK] saying, that, that is [MASK] fiscal policy can [MASK] that, really, monetary policy can’t do—is, is invest in the future productive capacity of [MASK] economy, raise potential growth.</t>
+          <t>We're looking at wages and we're looking [MASK] [MASK] inflation.</t>
         </is>
       </c>
       <c r="B706" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C706" t="n">
         <v>2</v>
@@ -15251,11 +15251,11 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>[MASK] let me talk [MASK] the coronavirus specifically, and [MASK] I’ll turn more to global growth more generally.</t>
+          <t>I’[MASK] [MASK] saying, that, that is [MASK] fiscal policy can [MASK] that, really, monetary policy can’t do—is, is invest in the future productive capacity of [MASK] economy, raise potential growth.</t>
         </is>
       </c>
       <c r="B707" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C707" t="n">
         <v>2</v>
@@ -15272,11 +15272,11 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>I did indicate [MASK] I do have concerns about the scope [MASK] monetary policy.</t>
+          <t>[MASK] let me talk [MASK] the coronavirus specifically, and [MASK] I’ll turn more to global growth more generally.</t>
         </is>
       </c>
       <c r="B708" t="n">
-        <v>2013</v>
+        <v>2019</v>
       </c>
       <c r="C708" t="n">
         <v>2</v>
@@ -15293,19 +15293,40 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
+          <t>I did indicate [MASK] I do have concerns about the scope [MASK] monetary policy.</t>
+        </is>
+      </c>
+      <c r="B709" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C709" t="n">
+        <v>2</v>
+      </c>
+      <c r="D709" t="n">
+        <v>1</v>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>masking</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
           <t>[MASK] central tendency rises to 2.4 to 2.7 percent [MASK] year, somewhat above estimates of the longer-run [MASK] rate.</t>
         </is>
       </c>
-      <c r="B709" t="n">
+      <c r="B710" t="n">
         <v>2012</v>
       </c>
-      <c r="C709" t="n">
-        <v>1</v>
-      </c>
-      <c r="D709" t="n">
-        <v>1</v>
-      </c>
-      <c r="E709" t="inlineStr">
+      <c r="C710" t="n">
+        <v>1</v>
+      </c>
+      <c r="D710" t="n">
+        <v>1</v>
+      </c>
+      <c r="E710" t="inlineStr">
         <is>
           <t>masking</t>
         </is>
